--- a/Business Analysis/6.1+Regression+analysis_before.xlsx
+++ b/Business Analysis/6.1+Regression+analysis_before.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Courses\Video creating\Enterprise excellence\Case study\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\Financial-Analysis\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBB121C-4AA5-4050-861F-546E331C488D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E3AFF1-C721-40EE-B791-22219B8C8799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="7" xr2:uid="{F12A9117-8F43-4D89-91AA-57E2FEF63FB4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="2" activeTab="7" xr2:uid="{F12A9117-8F43-4D89-91AA-57E2FEF63FB4}"/>
   </bookViews>
   <sheets>
     <sheet name="Database" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="63">
   <si>
     <t>Database</t>
   </si>
@@ -394,13 +394,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -423,34 +422,31 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,7 +561,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1269,6 +1265,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1276,7 +1273,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2206,23 +2202,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2368FC57-6F23-4732-A5C2-167A88E5ECC4}">
   <dimension ref="B1:L148"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="3" width="9.140625" style="1"/>
-    <col min="4" max="4" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="1"/>
-    <col min="6" max="6" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.1796875" style="1"/>
+    <col min="4" max="4" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1796875" style="1"/>
+    <col min="6" max="6" width="12.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.42578125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="19.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.453125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2230,49 +2226,49 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="J4" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="L4" s="24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B5" s="6">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>2019</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <f>EOMONTH(DATE(C5,B5,"1"),0)</f>
         <v>43496</v>
       </c>
@@ -2301,14 +2297,14 @@
         <v>69.025004250191103</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B6" s="6">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="5">
         <v>2</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>2019</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <f>EOMONTH(DATE(C6,B6,"1"),0)</f>
         <v>43524</v>
       </c>
@@ -2337,14 +2333,14 @@
         <v>57.520836875159247</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B7" s="6">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B7" s="5">
         <v>3</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>2019</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <f>EOMONTH(DATE(C7,B7,"1"),0)</f>
         <v>43555</v>
       </c>
@@ -2373,14 +2369,14 @@
         <v>60.851039057917099</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B8" s="6">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="5">
         <v>4</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>2019</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <f t="shared" ref="D8:D71" si="0">EOMONTH(DATE(C8,B8,"1"),0)</f>
         <v>43585</v>
       </c>
@@ -2409,14 +2405,14 @@
         <v>64.960981617215637</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B9" s="6">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B9" s="5">
         <v>5</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>2019</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <f t="shared" si="0"/>
         <v>43616</v>
       </c>
@@ -2445,14 +2441,14 @@
         <v>64.960981617215637</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B10" s="6">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="5">
         <v>6</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>2019</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <f t="shared" si="0"/>
         <v>43646</v>
       </c>
@@ -2481,14 +2477,14 @@
         <v>71.706858378858712</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B11" s="6">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B11" s="5">
         <v>7</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>2019</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <f t="shared" si="0"/>
         <v>43677</v>
       </c>
@@ -2517,14 +2513,14 @@
         <v>71.706858378858712</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B12" s="6">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="5">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>2019</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <f t="shared" si="0"/>
         <v>43708</v>
       </c>
@@ -2553,14 +2549,14 @@
         <v>71.706858378858712</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B13" s="6">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B13" s="5">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>2019</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <f t="shared" si="0"/>
         <v>43738</v>
       </c>
@@ -2589,14 +2585,14 @@
         <v>71.706858378858712</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B14" s="6">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
         <v>10</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <v>2019</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <f t="shared" si="0"/>
         <v>43769</v>
       </c>
@@ -2625,14 +2621,14 @@
         <v>68.706787320924349</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B15" s="6">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B15" s="5">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>2019</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <f t="shared" si="0"/>
         <v>43799</v>
       </c>
@@ -2661,14 +2657,14 @@
         <v>68.706787320924349</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B16" s="6">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B16" s="5">
         <v>12</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="5">
         <v>2019</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="10">
         <f t="shared" si="0"/>
         <v>43830</v>
       </c>
@@ -2697,14 +2693,14 @@
         <v>68.706787320924349</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B17" s="6">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B17" s="5">
         <v>1</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
         <v>2020</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="10">
         <f t="shared" si="0"/>
         <v>43861</v>
       </c>
@@ -2733,14 +2729,14 @@
         <v>78.155624371879711</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B18" s="6">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B18" s="5">
         <v>2</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
         <v>2020</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="10">
         <f t="shared" si="0"/>
         <v>43890</v>
       </c>
@@ -2769,14 +2765,14 @@
         <v>65.129686976566433</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B19" s="6">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B19" s="5">
         <v>3</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <v>2020</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="10">
         <f t="shared" si="0"/>
         <v>43921</v>
       </c>
@@ -2805,14 +2801,14 @@
         <v>75.274039028579637</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B20" s="6">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B20" s="5">
         <v>4</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <v>2020</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="10">
         <f t="shared" si="0"/>
         <v>43951</v>
       </c>
@@ -2841,14 +2837,14 @@
         <v>75.274039028579637</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B21" s="6">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B21" s="5">
         <v>5</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="5">
         <v>2020</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="10">
         <f t="shared" si="0"/>
         <v>43982</v>
       </c>
@@ -2877,14 +2873,14 @@
         <v>75.274039028579637</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B22" s="6">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B22" s="5">
         <v>6</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="5">
         <v>2020</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="10">
         <f t="shared" si="0"/>
         <v>44012</v>
       </c>
@@ -2913,14 +2909,14 @@
         <v>84.321941536768662</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B23" s="6">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B23" s="5">
         <v>7</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="5">
         <v>2020</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="10">
         <f t="shared" si="0"/>
         <v>44043</v>
       </c>
@@ -2949,14 +2945,14 @@
         <v>84.321941536768662</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B24" s="6">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B24" s="5">
         <v>8</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="5">
         <v>2020</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="10">
         <f t="shared" si="0"/>
         <v>44074</v>
       </c>
@@ -2985,14 +2981,14 @@
         <v>84.321941536768662</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="6">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B25" s="5">
         <v>9</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="5">
         <v>2020</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="10">
         <f t="shared" si="0"/>
         <v>44104</v>
       </c>
@@ -3021,14 +3017,14 @@
         <v>84.321941536768662</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B26" s="6">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B26" s="5">
         <v>10</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="5">
         <v>2020</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="10">
         <f t="shared" si="0"/>
         <v>44135</v>
       </c>
@@ -3057,14 +3053,14 @@
         <v>76.996142597335265</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B27" s="6">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B27" s="5">
         <v>11</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="5">
         <v>2020</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="10">
         <f t="shared" si="0"/>
         <v>44165</v>
       </c>
@@ -3093,14 +3089,14 @@
         <v>76.996142597335265</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B28" s="6">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B28" s="5">
         <v>12</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="5">
         <v>2020</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="10">
         <f t="shared" si="0"/>
         <v>44196</v>
       </c>
@@ -3129,14 +3125,14 @@
         <v>80.67956081669594</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B29" s="6">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B29" s="5">
         <v>1</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="5">
         <v>2021</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="10">
         <f t="shared" si="0"/>
         <v>44227</v>
       </c>
@@ -3165,14 +3161,14 @@
         <v>101.59504890398503</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B30" s="6">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B30" s="5">
         <v>2</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="5">
         <v>2021</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="10">
         <f t="shared" si="0"/>
         <v>44255</v>
       </c>
@@ -3201,14 +3197,14 @@
         <v>85.647647017909222</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B31" s="6">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B31" s="5">
         <v>3</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="5">
         <v>2021</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="10">
         <f t="shared" si="0"/>
         <v>44286</v>
       </c>
@@ -3237,14 +3233,14 @@
         <v>97.037630199114446</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B32" s="6">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B32" s="5">
         <v>4</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="5">
         <v>2021</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="10">
         <f t="shared" si="0"/>
         <v>44316</v>
       </c>
@@ -3273,14 +3269,14 @@
         <v>98.916233982605618</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B33" s="6">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B33" s="5">
         <v>5</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="5">
         <v>2021</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="10">
         <f t="shared" si="0"/>
         <v>44347</v>
       </c>
@@ -3309,14 +3305,14 @@
         <v>105.802493123179</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B34" s="6">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B34" s="5">
         <v>6</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="5">
         <v>2021</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="10">
         <f t="shared" si="0"/>
         <v>44377</v>
       </c>
@@ -3345,14 +3341,14 @@
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B35" s="6">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B35" s="5">
         <v>7</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="5">
         <v>2021</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="10">
         <f t="shared" si="0"/>
         <v>44408</v>
       </c>
@@ -3381,14 +3377,14 @@
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B36" s="6">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B36" s="5">
         <v>8</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="5">
         <v>2021</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="10">
         <f t="shared" si="0"/>
         <v>44439</v>
       </c>
@@ -3417,14 +3413,14 @@
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B37" s="6">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B37" s="5">
         <v>9</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="5">
         <v>2021</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="10">
         <f t="shared" si="0"/>
         <v>44469</v>
       </c>
@@ -3453,14 +3449,14 @@
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B38" s="6">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B38" s="5">
         <v>10</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="5">
         <v>2021</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="10">
         <f t="shared" si="0"/>
         <v>44500</v>
       </c>
@@ -3489,14 +3485,14 @@
         <v>102.40669860582705</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B39" s="6">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B39" s="5">
         <v>11</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="5">
         <v>2021</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="10">
         <f t="shared" si="0"/>
         <v>44530</v>
       </c>
@@ -3525,14 +3521,14 @@
         <v>102.40669860582705</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B40" s="6">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B40" s="5">
         <v>12</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="5">
         <v>2021</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="10">
         <f t="shared" si="0"/>
         <v>44561</v>
       </c>
@@ -3561,14 +3557,14 @@
         <v>99.258185203903267</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B41" s="6">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B41" s="5">
         <v>1</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="5">
         <v>2019</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="10">
         <f t="shared" si="0"/>
         <v>43496</v>
       </c>
@@ -3597,14 +3593,14 @@
         <v>2.9796847358460092</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B42" s="6">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B42" s="5">
         <v>2</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="5">
         <v>2019</v>
       </c>
-      <c r="D42" s="11">
+      <c r="D42" s="10">
         <f t="shared" si="0"/>
         <v>43524</v>
       </c>
@@ -3633,14 +3629,14 @@
         <v>3.2088912539880092</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B43" s="6">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B43" s="5">
         <v>3</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="5">
         <v>2019</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="10">
         <f t="shared" si="0"/>
         <v>43555</v>
       </c>
@@ -3669,14 +3665,14 @@
         <v>3.7655356551900114</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B44" s="6">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B44" s="5">
         <v>4</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="5">
         <v>2019</v>
       </c>
-      <c r="D44" s="11">
+      <c r="D44" s="10">
         <f t="shared" si="0"/>
         <v>43585</v>
       </c>
@@ -3705,14 +3701,14 @@
         <v>3.6673042902720114</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B45" s="6">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B45" s="5">
         <v>5</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="5">
         <v>2019</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="10">
         <f t="shared" si="0"/>
         <v>43616</v>
       </c>
@@ -3741,14 +3737,14 @@
         <v>4.082058942148012</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B46" s="6">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B46" s="5">
         <v>6</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="5">
         <v>2019</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="10">
         <f t="shared" si="0"/>
         <v>43646</v>
       </c>
@@ -3777,14 +3773,14 @@
         <v>4.3221800563920132</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B47" s="6">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B47" s="5">
         <v>7</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="5">
         <v>2019</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="10">
         <f t="shared" si="0"/>
         <v>43677</v>
       </c>
@@ -3813,14 +3809,14 @@
         <v>4.3549238446980123</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B48" s="6">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B48" s="5">
         <v>8</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48" s="5">
         <v>2019</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="10">
         <f t="shared" si="0"/>
         <v>43708</v>
       </c>
@@ -3849,14 +3845,14 @@
         <v>3.0560869085600095</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B49" s="6">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B49" s="5">
         <v>9</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49" s="5">
         <v>2019</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="10">
         <f t="shared" si="0"/>
         <v>43738</v>
       </c>
@@ -3885,14 +3881,14 @@
         <v>5.0425433991240149</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B50" s="6">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B50" s="5">
         <v>10</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50" s="5">
         <v>2019</v>
       </c>
-      <c r="D50" s="11">
+      <c r="D50" s="10">
         <f t="shared" si="0"/>
         <v>43769</v>
       </c>
@@ -3921,14 +3917,14 @@
         <v>5.0425433991240149</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B51" s="6">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B51" s="5">
         <v>11</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="5">
         <v>2019</v>
       </c>
-      <c r="D51" s="11">
+      <c r="D51" s="10">
         <f t="shared" si="0"/>
         <v>43799</v>
       </c>
@@ -3957,14 +3953,14 @@
         <v>5.5227856276120155</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B52" s="6">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B52" s="5">
         <v>12</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C52" s="5">
         <v>2019</v>
       </c>
-      <c r="D52" s="11">
+      <c r="D52" s="10">
         <f t="shared" si="0"/>
         <v>43830</v>
       </c>
@@ -3993,14 +3989,14 @@
         <v>5.7629067418560176</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B53" s="6">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B53" s="5">
         <v>1</v>
       </c>
-      <c r="C53" s="6">
+      <c r="C53" s="5">
         <v>2020</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="10">
         <f t="shared" si="0"/>
         <v>43861</v>
       </c>
@@ -4029,14 +4025,14 @@
         <v>7.2522649846028084</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B54" s="6">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B54" s="5">
         <v>2</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C54" s="5">
         <v>2020</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="10">
         <f t="shared" si="0"/>
         <v>43890</v>
       </c>
@@ -4065,14 +4061,14 @@
         <v>6.8566868945335635</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B55" s="6">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B55" s="5">
         <v>3</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55" s="5">
         <v>2020</v>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="10">
         <f t="shared" si="0"/>
         <v>43921</v>
       </c>
@@ -4101,14 +4097,14 @@
         <v>8.1884664644333505</v>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B56" s="6">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B56" s="5">
         <v>4</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56" s="5">
         <v>2020</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="10">
         <f t="shared" si="0"/>
         <v>43951</v>
       </c>
@@ -4137,14 +4133,14 @@
         <v>7.3841243479592205</v>
       </c>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B57" s="6">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B57" s="5">
         <v>5</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C57" s="5">
         <v>2020</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="10">
         <f t="shared" si="0"/>
         <v>43982</v>
       </c>
@@ -4173,14 +4169,14 @@
         <v>8.7950195358728571</v>
       </c>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B58" s="6">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B58" s="5">
         <v>6</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C58" s="5">
         <v>2020</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="10">
         <f t="shared" si="0"/>
         <v>44012</v>
       </c>
@@ -4209,14 +4205,14 @@
         <v>8.7027179815233673</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B59" s="6">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B59" s="5">
         <v>7</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59" s="5">
         <v>2020</v>
       </c>
-      <c r="D59" s="11">
+      <c r="D59" s="10">
         <f t="shared" si="0"/>
         <v>44043</v>
       </c>
@@ -4245,14 +4241,14 @@
         <v>8.5840445545025919</v>
       </c>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B60" s="6">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B60" s="5">
         <v>8</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60" s="5">
         <v>2020</v>
       </c>
-      <c r="D60" s="11">
+      <c r="D60" s="10">
         <f t="shared" si="0"/>
         <v>44074</v>
       </c>
@@ -4281,14 +4277,14 @@
         <v>5.907299478367376</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B61" s="6">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B61" s="5">
         <v>9</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C61" s="5">
         <v>2020</v>
       </c>
-      <c r="D61" s="11">
+      <c r="D61" s="10">
         <f t="shared" si="0"/>
         <v>44104</v>
       </c>
@@ -4317,14 +4313,14 @@
         <v>9.1378538805995326</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B62" s="6">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B62" s="5">
         <v>10</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="5">
         <v>2020</v>
       </c>
-      <c r="D62" s="11">
+      <c r="D62" s="10">
         <f t="shared" si="0"/>
         <v>44135</v>
       </c>
@@ -4353,14 +4349,14 @@
         <v>9.8630803790598129</v>
       </c>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B63" s="6">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B63" s="5">
         <v>11</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C63" s="5">
         <v>2020</v>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="10">
         <f t="shared" si="0"/>
         <v>44165</v>
       </c>
@@ -4389,14 +4385,14 @@
         <v>10.153170978443926</v>
       </c>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B64" s="6">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B64" s="5">
         <v>12</v>
       </c>
-      <c r="C64" s="6">
+      <c r="C64" s="5">
         <v>2020</v>
       </c>
-      <c r="D64" s="11">
+      <c r="D64" s="10">
         <f t="shared" si="0"/>
         <v>44196</v>
       </c>
@@ -4425,14 +4421,14 @@
         <v>9.96856786974495</v>
       </c>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B65" s="6">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B65" s="5">
         <v>1</v>
       </c>
-      <c r="C65" s="6">
+      <c r="C65" s="5">
         <v>2021</v>
       </c>
-      <c r="D65" s="11">
+      <c r="D65" s="10">
         <f t="shared" si="0"/>
         <v>44227</v>
       </c>
@@ -4461,14 +4457,14 @@
         <v>13.236524206212621</v>
       </c>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B66" s="6">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B66" s="5">
         <v>2</v>
       </c>
-      <c r="C66" s="6">
+      <c r="C66" s="5">
         <v>2021</v>
       </c>
-      <c r="D66" s="11">
+      <c r="D66" s="10">
         <f t="shared" si="0"/>
         <v>44255</v>
       </c>
@@ -4497,14 +4493,14 @@
         <v>11.821102698850286</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B67" s="6">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B67" s="5">
         <v>3</v>
       </c>
-      <c r="C67" s="6">
+      <c r="C67" s="5">
         <v>2021</v>
       </c>
-      <c r="D67" s="11">
+      <c r="D67" s="10">
         <f t="shared" si="0"/>
         <v>44286</v>
       </c>
@@ -4533,14 +4529,14 @@
         <v>13.345402783702031</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B68" s="6">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B68" s="5">
         <v>4</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C68" s="5">
         <v>2021</v>
       </c>
-      <c r="D68" s="11">
+      <c r="D68" s="10">
         <f t="shared" si="0"/>
         <v>44316</v>
       </c>
@@ -4569,14 +4565,14 @@
         <v>13.065429298729258</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B69" s="6">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B69" s="5">
         <v>5</v>
       </c>
-      <c r="C69" s="6">
+      <c r="C69" s="5">
         <v>2021</v>
       </c>
-      <c r="D69" s="11">
+      <c r="D69" s="10">
         <f t="shared" si="0"/>
         <v>44347</v>
       </c>
@@ -4605,14 +4601,14 @@
         <v>14.667499796073445</v>
       </c>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B70" s="6">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B70" s="5">
         <v>6</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C70" s="5">
         <v>2021</v>
       </c>
-      <c r="D70" s="11">
+      <c r="D70" s="10">
         <f t="shared" si="0"/>
         <v>44377</v>
       </c>
@@ -4641,14 +4637,14 @@
         <v>13.718700763665721</v>
       </c>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B71" s="6">
+    <row r="71" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B71" s="5">
         <v>7</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C71" s="5">
         <v>2021</v>
       </c>
-      <c r="D71" s="11">
+      <c r="D71" s="10">
         <f t="shared" si="0"/>
         <v>44408</v>
       </c>
@@ -4677,14 +4673,14 @@
         <v>14.714162043568905</v>
       </c>
     </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B72" s="6">
+    <row r="72" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B72" s="5">
         <v>8</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C72" s="5">
         <v>2021</v>
       </c>
-      <c r="D72" s="11">
+      <c r="D72" s="10">
         <f t="shared" ref="D72:D135" si="1">EOMONTH(DATE(C72,B72,"1"),0)</f>
         <v>44439</v>
       </c>
@@ -4713,14 +4709,14 @@
         <v>9.5813148190681225</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B73" s="6">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B73" s="5">
         <v>9</v>
       </c>
-      <c r="C73" s="6">
+      <c r="C73" s="5">
         <v>2021</v>
       </c>
-      <c r="D73" s="11">
+      <c r="D73" s="10">
         <f t="shared" si="1"/>
         <v>44469</v>
       </c>
@@ -4749,14 +4745,14 @@
         <v>13.998674248638491</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B74" s="6">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B74" s="5">
         <v>10</v>
       </c>
-      <c r="C74" s="6">
+      <c r="C74" s="5">
         <v>2021</v>
       </c>
-      <c r="D74" s="11">
+      <c r="D74" s="10">
         <f t="shared" si="1"/>
         <v>44500</v>
       </c>
@@ -4785,14 +4781,14 @@
         <v>16.45621928339947</v>
       </c>
     </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B75" s="6">
+    <row r="75" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B75" s="5">
         <v>11</v>
       </c>
-      <c r="C75" s="6">
+      <c r="C75" s="5">
         <v>2021</v>
       </c>
-      <c r="D75" s="11">
+      <c r="D75" s="10">
         <f t="shared" si="1"/>
         <v>44530</v>
       </c>
@@ -4821,14 +4817,14 @@
         <v>16.082921303435779</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B76" s="6">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B76" s="5">
         <v>12</v>
       </c>
-      <c r="C76" s="6">
+      <c r="C76" s="5">
         <v>2021</v>
       </c>
-      <c r="D76" s="11">
+      <c r="D76" s="10">
         <f t="shared" si="1"/>
         <v>44561</v>
       </c>
@@ -4857,14 +4853,14 @@
         <v>15.678515158475117</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B77" s="6">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B77" s="5">
         <v>1</v>
       </c>
-      <c r="C77" s="6">
+      <c r="C77" s="5">
         <v>2019</v>
       </c>
-      <c r="D77" s="11">
+      <c r="D77" s="10">
         <f t="shared" si="1"/>
         <v>43496</v>
       </c>
@@ -4893,14 +4889,14 @@
         <v>2.5124397260372198</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B78" s="6">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B78" s="5">
         <v>2</v>
       </c>
-      <c r="C78" s="6">
+      <c r="C78" s="5">
         <v>2019</v>
       </c>
-      <c r="D78" s="11">
+      <c r="D78" s="10">
         <f t="shared" si="1"/>
         <v>43524</v>
       </c>
@@ -4929,14 +4925,14 @@
         <v>2.7057043203477753</v>
       </c>
     </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B79" s="6">
+    <row r="79" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B79" s="5">
         <v>3</v>
       </c>
-      <c r="C79" s="6">
+      <c r="C79" s="5">
         <v>2019</v>
       </c>
-      <c r="D79" s="11">
+      <c r="D79" s="10">
         <f t="shared" si="1"/>
         <v>43555</v>
       </c>
@@ -4965,14 +4961,14 @@
         <v>3.1750611922448386</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B80" s="6">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B80" s="5">
         <v>4</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C80" s="5">
         <v>2019</v>
       </c>
-      <c r="D80" s="11">
+      <c r="D80" s="10">
         <f t="shared" si="1"/>
         <v>43585</v>
       </c>
@@ -5001,14 +4997,14 @@
         <v>3.0922335089688859</v>
       </c>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B81" s="6">
+    <row r="81" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B81" s="5">
         <v>5</v>
       </c>
-      <c r="C81" s="6">
+      <c r="C81" s="5">
         <v>2019</v>
       </c>
-      <c r="D81" s="11">
+      <c r="D81" s="10">
         <f t="shared" si="1"/>
         <v>43616</v>
       </c>
@@ -5037,14 +5033,14 @@
         <v>3.4419503939117955</v>
       </c>
     </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B82" s="6">
+    <row r="82" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B82" s="5">
         <v>6</v>
       </c>
-      <c r="C82" s="6">
+      <c r="C82" s="5">
         <v>2019</v>
       </c>
-      <c r="D82" s="11">
+      <c r="D82" s="10">
         <f t="shared" si="1"/>
         <v>43646</v>
       </c>
@@ -5073,14 +5069,14 @@
         <v>3.6444180641419015</v>
       </c>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B83" s="6">
+    <row r="83" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B83" s="5">
         <v>7</v>
       </c>
-      <c r="C83" s="6">
+      <c r="C83" s="5">
         <v>2019</v>
       </c>
-      <c r="D83" s="11">
+      <c r="D83" s="10">
         <f t="shared" si="1"/>
         <v>43677</v>
       </c>
@@ -5109,14 +5105,14 @@
         <v>3.6720272919005521</v>
       </c>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B84" s="6">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B84" s="5">
         <v>8</v>
       </c>
-      <c r="C84" s="6">
+      <c r="C84" s="5">
         <v>2019</v>
       </c>
-      <c r="D84" s="11">
+      <c r="D84" s="10">
         <f t="shared" si="1"/>
         <v>43708</v>
       </c>
@@ -5145,14 +5141,14 @@
         <v>2.5768612574740724</v>
       </c>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B85" s="6">
+    <row r="85" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B85" s="5">
         <v>9</v>
       </c>
-      <c r="C85" s="6">
+      <c r="C85" s="5">
         <v>2019</v>
       </c>
-      <c r="D85" s="11">
+      <c r="D85" s="10">
         <f t="shared" si="1"/>
         <v>43738</v>
       </c>
@@ -5181,14 +5177,14 @@
         <v>4.2518210748322174</v>
       </c>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B86" s="6">
+    <row r="86" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B86" s="5">
         <v>10</v>
       </c>
-      <c r="C86" s="6">
+      <c r="C86" s="5">
         <v>2019</v>
       </c>
-      <c r="D86" s="11">
+      <c r="D86" s="10">
         <f t="shared" si="1"/>
         <v>43769</v>
       </c>
@@ -5217,14 +5213,14 @@
         <v>4.2518210748322174</v>
       </c>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B87" s="6">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B87" s="5">
         <v>11</v>
       </c>
-      <c r="C87" s="6">
+      <c r="C87" s="5">
         <v>2019</v>
       </c>
-      <c r="D87" s="11">
+      <c r="D87" s="10">
         <f t="shared" si="1"/>
         <v>43799</v>
       </c>
@@ -5253,14 +5249,14 @@
         <v>4.6567564152924295</v>
       </c>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B88" s="6">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B88" s="5">
         <v>12</v>
       </c>
-      <c r="C88" s="6">
+      <c r="C88" s="5">
         <v>2019</v>
       </c>
-      <c r="D88" s="11">
+      <c r="D88" s="10">
         <f t="shared" si="1"/>
         <v>43830</v>
       </c>
@@ -5289,14 +5285,14 @@
         <v>4.8592240855225359</v>
       </c>
     </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B89" s="6">
+    <row r="89" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B89" s="5">
         <v>1</v>
       </c>
-      <c r="C89" s="6">
+      <c r="C89" s="5">
         <v>2020</v>
       </c>
-      <c r="D89" s="11">
+      <c r="D89" s="10">
         <f t="shared" si="1"/>
         <v>43861</v>
       </c>
@@ -5325,14 +5321,14 @@
         <v>5.9873962294839496</v>
       </c>
     </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B90" s="6">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B90" s="5">
         <v>2</v>
       </c>
-      <c r="C90" s="6">
+      <c r="C90" s="5">
         <v>2020</v>
       </c>
-      <c r="D90" s="11">
+      <c r="D90" s="10">
         <f t="shared" si="1"/>
         <v>43890</v>
       </c>
@@ -5361,14 +5357,14 @@
         <v>5.6608109806030038</v>
       </c>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B91" s="6">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B91" s="5">
         <v>3</v>
       </c>
-      <c r="C91" s="6">
+      <c r="C91" s="5">
         <v>2020</v>
       </c>
-      <c r="D91" s="11">
+      <c r="D91" s="10">
         <f t="shared" si="1"/>
         <v>43921</v>
       </c>
@@ -5397,14 +5393,14 @@
         <v>6.7603146518355102</v>
       </c>
     </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B92" s="6">
+    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B92" s="5">
         <v>4</v>
       </c>
-      <c r="C92" s="6">
+      <c r="C92" s="5">
         <v>2020</v>
       </c>
-      <c r="D92" s="11">
+      <c r="D92" s="10">
         <f t="shared" si="1"/>
         <v>43951</v>
       </c>
@@ -5433,14 +5429,14 @@
         <v>6.0962579791109262</v>
       </c>
     </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B93" s="6">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B93" s="5">
         <v>5</v>
       </c>
-      <c r="C93" s="6">
+      <c r="C93" s="5">
         <v>2020</v>
       </c>
-      <c r="D93" s="11">
+      <c r="D93" s="10">
         <f t="shared" si="1"/>
         <v>43982</v>
       </c>
@@ -5469,14 +5465,14 @@
         <v>7.2610787001196222</v>
       </c>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B94" s="6">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B94" s="5">
         <v>6</v>
       </c>
-      <c r="C94" s="6">
+      <c r="C94" s="5">
         <v>2020</v>
       </c>
-      <c r="D94" s="11">
+      <c r="D94" s="10">
         <f t="shared" si="1"/>
         <v>44012</v>
       </c>
@@ -5505,14 +5501,14 @@
         <v>7.1848754753807356</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B95" s="6">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B95" s="5">
         <v>7</v>
       </c>
-      <c r="C95" s="6">
+      <c r="C95" s="5">
         <v>2020</v>
       </c>
-      <c r="D95" s="11">
+      <c r="D95" s="10">
         <f t="shared" si="1"/>
         <v>44043</v>
       </c>
@@ -5541,14 +5537,14 @@
         <v>7.0868999007164515</v>
       </c>
     </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B96" s="6">
+    <row r="96" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B96" s="5">
         <v>8</v>
       </c>
-      <c r="C96" s="6">
+      <c r="C96" s="5">
         <v>2020</v>
       </c>
-      <c r="D96" s="11">
+      <c r="D96" s="10">
         <f t="shared" si="1"/>
         <v>44074</v>
       </c>
@@ -5577,14 +5573,14 @@
         <v>4.8770063832887409</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B97" s="6">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B97" s="5">
         <v>9</v>
       </c>
-      <c r="C97" s="6">
+      <c r="C97" s="5">
         <v>2020</v>
       </c>
-      <c r="D97" s="11">
+      <c r="D97" s="10">
         <f t="shared" si="1"/>
         <v>44104</v>
       </c>
@@ -5613,14 +5609,14 @@
         <v>7.5441192491497713</v>
       </c>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B98" s="6">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B98" s="5">
         <v>10</v>
       </c>
-      <c r="C98" s="6">
+      <c r="C98" s="5">
         <v>2020</v>
       </c>
-      <c r="D98" s="11">
+      <c r="D98" s="10">
         <f t="shared" si="1"/>
         <v>44135</v>
       </c>
@@ -5649,14 +5645,14 @@
         <v>8.1428588720981647</v>
       </c>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B99" s="6">
+    <row r="99" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B99" s="5">
         <v>11</v>
       </c>
-      <c r="C99" s="6">
+      <c r="C99" s="5">
         <v>2020</v>
       </c>
-      <c r="D99" s="11">
+      <c r="D99" s="10">
         <f t="shared" si="1"/>
         <v>44165</v>
       </c>
@@ -5685,14 +5681,14 @@
         <v>8.382354721277526</v>
       </c>
     </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B100" s="6">
+    <row r="100" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B100" s="5">
         <v>12</v>
       </c>
-      <c r="C100" s="6">
+      <c r="C100" s="5">
         <v>2020</v>
       </c>
-      <c r="D100" s="11">
+      <c r="D100" s="10">
         <f t="shared" si="1"/>
         <v>44196</v>
       </c>
@@ -5721,14 +5717,14 @@
         <v>8.2299482717997527</v>
       </c>
     </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B101" s="6">
+    <row r="101" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B101" s="5">
         <v>1</v>
       </c>
-      <c r="C101" s="6">
+      <c r="C101" s="5">
         <v>2021</v>
       </c>
-      <c r="D101" s="11">
+      <c r="D101" s="10">
         <f t="shared" si="1"/>
         <v>44227</v>
       </c>
@@ -5757,14 +5753,14 @@
         <v>10.737220126311428</v>
       </c>
     </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B102" s="6">
+    <row r="102" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B102" s="5">
         <v>2</v>
       </c>
-      <c r="C102" s="6">
+      <c r="C102" s="5">
         <v>2021</v>
       </c>
-      <c r="D102" s="11">
+      <c r="D102" s="10">
         <f t="shared" si="1"/>
         <v>44255</v>
       </c>
@@ -5793,14 +5789,14 @@
         <v>9.5890567520525085</v>
       </c>
     </row>
-    <row r="103" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B103" s="6">
+    <row r="103" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B103" s="5">
         <v>3</v>
       </c>
-      <c r="C103" s="6">
+      <c r="C103" s="5">
         <v>2021</v>
       </c>
-      <c r="D103" s="11">
+      <c r="D103" s="10">
         <f t="shared" si="1"/>
         <v>44286</v>
       </c>
@@ -5829,14 +5825,14 @@
         <v>10.825540385869804</v>
       </c>
     </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B104" s="6">
+    <row r="104" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B104" s="5">
         <v>4</v>
       </c>
-      <c r="C104" s="6">
+      <c r="C104" s="5">
         <v>2021</v>
       </c>
-      <c r="D104" s="11">
+      <c r="D104" s="10">
         <f t="shared" si="1"/>
         <v>44316</v>
       </c>
@@ -5865,14 +5861,14 @@
         <v>10.598431147005403</v>
       </c>
     </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B105" s="6">
+    <row r="105" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B105" s="5">
         <v>5</v>
       </c>
-      <c r="C105" s="6">
+      <c r="C105" s="5">
         <v>2021</v>
       </c>
-      <c r="D105" s="11">
+      <c r="D105" s="10">
         <f t="shared" si="1"/>
         <v>44347</v>
       </c>
@@ -5901,14 +5897,14 @@
         <v>11.898000680507254</v>
       </c>
     </row>
-    <row r="106" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B106" s="6">
+    <row r="106" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B106" s="5">
         <v>6</v>
       </c>
-      <c r="C106" s="6">
+      <c r="C106" s="5">
         <v>2021</v>
       </c>
-      <c r="D106" s="11">
+      <c r="D106" s="10">
         <f t="shared" si="1"/>
         <v>44377</v>
       </c>
@@ -5937,14 +5933,14 @@
         <v>11.128352704355672</v>
       </c>
     </row>
-    <row r="107" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B107" s="6">
+    <row r="107" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B107" s="5">
         <v>7</v>
       </c>
-      <c r="C107" s="6">
+      <c r="C107" s="5">
         <v>2021</v>
       </c>
-      <c r="D107" s="11">
+      <c r="D107" s="10">
         <f t="shared" si="1"/>
         <v>44408</v>
       </c>
@@ -5973,14 +5969,14 @@
         <v>11.935852220317987</v>
       </c>
     </row>
-    <row r="108" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B108" s="6">
+    <row r="108" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B108" s="5">
         <v>8</v>
       </c>
-      <c r="C108" s="6">
+      <c r="C108" s="5">
         <v>2021</v>
       </c>
-      <c r="D108" s="11">
+      <c r="D108" s="10">
         <f t="shared" si="1"/>
         <v>44439</v>
       </c>
@@ -6009,14 +6005,14 @@
         <v>7.772182841137294</v>
       </c>
     </row>
-    <row r="109" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B109" s="6">
+    <row r="109" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B109" s="5">
         <v>9</v>
       </c>
-      <c r="C109" s="6">
+      <c r="C109" s="5">
         <v>2021</v>
       </c>
-      <c r="D109" s="11">
+      <c r="D109" s="10">
         <f t="shared" si="1"/>
         <v>44469</v>
       </c>
@@ -6045,14 +6041,14 @@
         <v>11.355461943220073</v>
       </c>
     </row>
-    <row r="110" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B110" s="6">
+    <row r="110" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B110" s="5">
         <v>10</v>
       </c>
-      <c r="C110" s="6">
+      <c r="C110" s="5">
         <v>2021</v>
       </c>
-      <c r="D110" s="11">
+      <c r="D110" s="10">
         <f t="shared" si="1"/>
         <v>44500</v>
       </c>
@@ -6081,14 +6077,14 @@
         <v>13.348976373252041</v>
       </c>
     </row>
-    <row r="111" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B111" s="6">
+    <row r="111" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B111" s="5">
         <v>11</v>
       </c>
-      <c r="C111" s="6">
+      <c r="C111" s="5">
         <v>2021</v>
       </c>
-      <c r="D111" s="11">
+      <c r="D111" s="10">
         <f t="shared" si="1"/>
         <v>44530</v>
       </c>
@@ -6117,14 +6113,14 @@
         <v>13.046164054766171</v>
       </c>
     </row>
-    <row r="112" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B112" s="6">
+    <row r="112" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B112" s="5">
         <v>12</v>
       </c>
-      <c r="C112" s="6">
+      <c r="C112" s="5">
         <v>2021</v>
       </c>
-      <c r="D112" s="11">
+      <c r="D112" s="10">
         <f t="shared" si="1"/>
         <v>44561</v>
       </c>
@@ -6153,14 +6149,14 @@
         <v>12.718117376406488</v>
       </c>
     </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B113" s="6">
+    <row r="113" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B113" s="5">
         <v>1</v>
       </c>
-      <c r="C113" s="6">
+      <c r="C113" s="5">
         <v>2019</v>
       </c>
-      <c r="D113" s="11">
+      <c r="D113" s="10">
         <f t="shared" si="1"/>
         <v>43496</v>
       </c>
@@ -6189,14 +6185,14 @@
         <v>5.0927506849621826</v>
       </c>
     </row>
-    <row r="114" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B114" s="6">
+    <row r="114" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B114" s="5">
         <v>2</v>
       </c>
-      <c r="C114" s="6">
+      <c r="C114" s="5">
         <v>2019</v>
       </c>
-      <c r="D114" s="11">
+      <c r="D114" s="10">
         <f t="shared" si="1"/>
         <v>43524</v>
       </c>
@@ -6225,14 +6221,14 @@
         <v>6.8111205198607507</v>
       </c>
     </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B115" s="6">
+    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B115" s="5">
         <v>3</v>
       </c>
-      <c r="C115" s="6">
+      <c r="C115" s="5">
         <v>2019</v>
       </c>
-      <c r="D115" s="11">
+      <c r="D115" s="10">
         <f t="shared" si="1"/>
         <v>43555</v>
       </c>
@@ -6261,14 +6257,14 @@
         <v>10.312070251557737</v>
       </c>
     </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B116" s="6">
+    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B116" s="5">
         <v>4</v>
       </c>
-      <c r="C116" s="6">
+      <c r="C116" s="5">
         <v>2019</v>
       </c>
-      <c r="D116" s="11">
+      <c r="D116" s="10">
         <f t="shared" si="1"/>
         <v>43585</v>
       </c>
@@ -6297,14 +6293,14 @@
         <v>9.0699708680454449</v>
       </c>
     </row>
-    <row r="117" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B117" s="6">
+    <row r="117" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B117" s="5">
         <v>5</v>
       </c>
-      <c r="C117" s="6">
+      <c r="C117" s="5">
         <v>2019</v>
       </c>
-      <c r="D117" s="11">
+      <c r="D117" s="10">
         <f t="shared" si="1"/>
         <v>43616</v>
       </c>
@@ -6333,14 +6329,14 @@
         <v>9.2450190868322792</v>
       </c>
     </row>
-    <row r="118" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B118" s="6">
+    <row r="118" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B118" s="5">
         <v>6</v>
       </c>
-      <c r="C118" s="6">
+      <c r="C118" s="5">
         <v>2019</v>
       </c>
-      <c r="D118" s="11">
+      <c r="D118" s="10">
         <f t="shared" si="1"/>
         <v>43646</v>
       </c>
@@ -6369,14 +6365,14 @@
         <v>9.4680150042305797</v>
       </c>
     </row>
-    <row r="119" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B119" s="6">
+    <row r="119" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B119" s="5">
         <v>7</v>
       </c>
-      <c r="C119" s="6">
+      <c r="C119" s="5">
         <v>2019</v>
       </c>
-      <c r="D119" s="11">
+      <c r="D119" s="10">
         <f t="shared" si="1"/>
         <v>43677</v>
       </c>
@@ -6405,14 +6401,14 @@
         <v>7.4921779038167768</v>
       </c>
     </row>
-    <row r="120" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B120" s="6">
+    <row r="120" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B120" s="5">
         <v>8</v>
       </c>
-      <c r="C120" s="6">
+      <c r="C120" s="5">
         <v>2019</v>
       </c>
-      <c r="D120" s="11">
+      <c r="D120" s="10">
         <f t="shared" si="1"/>
         <v>43708</v>
       </c>
@@ -6441,14 +6437,14 @@
         <v>5.3109476024213489</v>
       </c>
     </row>
-    <row r="121" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B121" s="6">
+    <row r="121" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B121" s="5">
         <v>9</v>
       </c>
-      <c r="C121" s="6">
+      <c r="C121" s="5">
         <v>2019</v>
       </c>
-      <c r="D121" s="11">
+      <c r="D121" s="10">
         <f t="shared" si="1"/>
         <v>43738</v>
       </c>
@@ -6477,14 +6473,14 @@
         <v>10.316668058759298</v>
       </c>
     </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B122" s="6">
+    <row r="122" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B122" s="5">
         <v>10</v>
       </c>
-      <c r="C122" s="6">
+      <c r="C122" s="5">
         <v>2019</v>
       </c>
-      <c r="D122" s="11">
+      <c r="D122" s="10">
         <f t="shared" si="1"/>
         <v>43769</v>
       </c>
@@ -6513,14 +6509,14 @@
         <v>11.670156305808623</v>
       </c>
     </row>
-    <row r="123" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B123" s="6">
+    <row r="123" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B123" s="5">
         <v>11</v>
       </c>
-      <c r="C123" s="6">
+      <c r="C123" s="5">
         <v>2019</v>
       </c>
-      <c r="D123" s="11">
+      <c r="D123" s="10">
         <f t="shared" si="1"/>
         <v>43799</v>
       </c>
@@ -6549,14 +6545,14 @@
         <v>13.518131529598255</v>
       </c>
     </row>
-    <row r="124" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B124" s="6">
+    <row r="124" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B124" s="5">
         <v>12</v>
       </c>
-      <c r="C124" s="6">
+      <c r="C124" s="5">
         <v>2019</v>
       </c>
-      <c r="D124" s="11">
+      <c r="D124" s="10">
         <f t="shared" si="1"/>
         <v>43830</v>
       </c>
@@ -6585,14 +6581,14 @@
         <v>9.2735534923399623</v>
       </c>
     </row>
-    <row r="125" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B125" s="6">
+    <row r="125" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B125" s="5">
         <v>1</v>
       </c>
-      <c r="C125" s="6">
+      <c r="C125" s="5">
         <v>2020</v>
       </c>
-      <c r="D125" s="11">
+      <c r="D125" s="10">
         <f t="shared" si="1"/>
         <v>43861</v>
       </c>
@@ -6621,14 +6617,14 @@
         <v>6.7970741697009123</v>
       </c>
     </row>
-    <row r="126" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B126" s="6">
+    <row r="126" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B126" s="5">
         <v>2</v>
       </c>
-      <c r="C126" s="6">
+      <c r="C126" s="5">
         <v>2020</v>
       </c>
-      <c r="D126" s="11">
+      <c r="D126" s="10">
         <f t="shared" si="1"/>
         <v>43890</v>
       </c>
@@ -6657,14 +6653,14 @@
         <v>7.8578934918565615</v>
       </c>
     </row>
-    <row r="127" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B127" s="6">
+    <row r="127" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B127" s="5">
         <v>3</v>
       </c>
-      <c r="C127" s="6">
+      <c r="C127" s="5">
         <v>2020</v>
       </c>
-      <c r="D127" s="11">
+      <c r="D127" s="10">
         <f t="shared" si="1"/>
         <v>43921</v>
       </c>
@@ -6693,14 +6689,14 @@
         <v>12.641561343069679</v>
       </c>
     </row>
-    <row r="128" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B128" s="6">
+    <row r="128" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B128" s="5">
         <v>4</v>
       </c>
-      <c r="C128" s="6">
+      <c r="C128" s="5">
         <v>2020</v>
       </c>
-      <c r="D128" s="11">
+      <c r="D128" s="10">
         <f t="shared" si="1"/>
         <v>43951</v>
       </c>
@@ -6729,14 +6725,14 @@
         <v>10.568561460047512</v>
       </c>
     </row>
-    <row r="129" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B129" s="6">
+    <row r="129" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B129" s="5">
         <v>5</v>
       </c>
-      <c r="C129" s="6">
+      <c r="C129" s="5">
         <v>2020</v>
       </c>
-      <c r="D129" s="11">
+      <c r="D129" s="10">
         <f t="shared" si="1"/>
         <v>43982</v>
       </c>
@@ -6765,14 +6761,14 @@
         <v>11.784181002365107</v>
       </c>
     </row>
-    <row r="130" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B130" s="6">
+    <row r="130" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B130" s="5">
         <v>6</v>
       </c>
-      <c r="C130" s="6">
+      <c r="C130" s="5">
         <v>2020</v>
       </c>
-      <c r="D130" s="11">
+      <c r="D130" s="10">
         <f t="shared" si="1"/>
         <v>44012</v>
       </c>
@@ -6801,14 +6797,14 @@
         <v>11.50460052489913</v>
       </c>
     </row>
-    <row r="131" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B131" s="6">
+    <row r="131" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B131" s="5">
         <v>7</v>
       </c>
-      <c r="C131" s="6">
+      <c r="C131" s="5">
         <v>2020</v>
       </c>
-      <c r="D131" s="11">
+      <c r="D131" s="10">
         <f t="shared" si="1"/>
         <v>44043</v>
       </c>
@@ -6837,14 +6833,14 @@
         <v>9.0771045199016118</v>
       </c>
     </row>
-    <row r="132" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B132" s="6">
+    <row r="132" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B132" s="5">
         <v>8</v>
       </c>
-      <c r="C132" s="6">
+      <c r="C132" s="5">
         <v>2020</v>
       </c>
-      <c r="D132" s="11">
+      <c r="D132" s="10">
         <f t="shared" si="1"/>
         <v>44074</v>
       </c>
@@ -6873,14 +6869,14 @@
         <v>6.4156636052953733</v>
       </c>
     </row>
-    <row r="133" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B133" s="6">
+    <row r="133" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B133" s="5">
         <v>9</v>
       </c>
-      <c r="C133" s="6">
+      <c r="C133" s="5">
         <v>2020</v>
       </c>
-      <c r="D133" s="11">
+      <c r="D133" s="10">
         <f t="shared" si="1"/>
         <v>44104</v>
       </c>
@@ -6909,14 +6905,14 @@
         <v>11.908918774645899</v>
       </c>
     </row>
-    <row r="134" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B134" s="6">
+    <row r="134" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B134" s="5">
         <v>10</v>
       </c>
-      <c r="C134" s="6">
+      <c r="C134" s="5">
         <v>2020</v>
       </c>
-      <c r="D134" s="11">
+      <c r="D134" s="10">
         <f t="shared" si="1"/>
         <v>44135</v>
       </c>
@@ -6945,14 +6941,14 @@
         <v>14.53319806860838</v>
       </c>
     </row>
-    <row r="135" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B135" s="6">
+    <row r="135" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B135" s="5">
         <v>11</v>
       </c>
-      <c r="C135" s="6">
+      <c r="C135" s="5">
         <v>2020</v>
       </c>
-      <c r="D135" s="11">
+      <c r="D135" s="10">
         <f t="shared" si="1"/>
         <v>44165</v>
       </c>
@@ -6981,14 +6977,14 @@
         <v>16.188214233067796</v>
       </c>
     </row>
-    <row r="136" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B136" s="6">
+    <row r="136" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B136" s="5">
         <v>12</v>
       </c>
-      <c r="C136" s="6">
+      <c r="C136" s="5">
         <v>2020</v>
       </c>
-      <c r="D136" s="11">
+      <c r="D136" s="10">
         <f t="shared" ref="D136:D148" si="2">EOMONTH(DATE(C136,B136,"1"),0)</f>
         <v>44196</v>
       </c>
@@ -7017,14 +7013,14 @@
         <v>10.555823944863995</v>
       </c>
     </row>
-    <row r="137" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B137" s="6">
+    <row r="137" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B137" s="5">
         <v>1</v>
       </c>
-      <c r="C137" s="6">
+      <c r="C137" s="5">
         <v>2021</v>
       </c>
-      <c r="D137" s="11">
+      <c r="D137" s="10">
         <f t="shared" si="2"/>
         <v>44227</v>
       </c>
@@ -7053,14 +7049,14 @@
         <v>8.5315813046451812</v>
       </c>
     </row>
-    <row r="138" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B138" s="6">
+    <row r="138" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B138" s="5">
         <v>2</v>
       </c>
-      <c r="C138" s="6">
+      <c r="C138" s="5">
         <v>2021</v>
       </c>
-      <c r="D138" s="11">
+      <c r="D138" s="10">
         <f t="shared" si="2"/>
         <v>44255</v>
       </c>
@@ -7089,14 +7085,14 @@
         <v>9.1851774604645069</v>
       </c>
     </row>
-    <row r="139" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B139" s="6">
+    <row r="139" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B139" s="5">
         <v>3</v>
       </c>
-      <c r="C139" s="6">
+      <c r="C139" s="5">
         <v>2021</v>
       </c>
-      <c r="D139" s="11">
+      <c r="D139" s="10">
         <f t="shared" si="2"/>
         <v>44286</v>
       </c>
@@ -7125,14 +7121,14 @@
         <v>14.20201699623775</v>
       </c>
     </row>
-    <row r="140" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B140" s="6">
+    <row r="140" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B140" s="5">
         <v>4</v>
       </c>
-      <c r="C140" s="6">
+      <c r="C140" s="5">
         <v>2021</v>
       </c>
-      <c r="D140" s="11">
+      <c r="D140" s="10">
         <f t="shared" si="2"/>
         <v>44316</v>
       </c>
@@ -7161,14 +7157,14 @@
         <v>13.011753250517556</v>
       </c>
     </row>
-    <row r="141" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B141" s="6">
+    <row r="141" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B141" s="5">
         <v>5</v>
       </c>
-      <c r="C141" s="6">
+      <c r="C141" s="5">
         <v>2021</v>
       </c>
-      <c r="D141" s="11">
+      <c r="D141" s="10">
         <f t="shared" si="2"/>
         <v>44347</v>
       </c>
@@ -7197,14 +7193,14 @@
         <v>13.859429457000086</v>
       </c>
     </row>
-    <row r="142" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B142" s="6">
+    <row r="142" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B142" s="5">
         <v>6</v>
       </c>
-      <c r="C142" s="6">
+      <c r="C142" s="5">
         <v>2021</v>
       </c>
-      <c r="D142" s="11">
+      <c r="D142" s="10">
         <f t="shared" si="2"/>
         <v>44377</v>
       </c>
@@ -7233,14 +7229,14 @@
         <v>12.948386515999688</v>
       </c>
     </row>
-    <row r="143" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B143" s="6">
+    <row r="143" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B143" s="5">
         <v>7</v>
       </c>
-      <c r="C143" s="6">
+      <c r="C143" s="5">
         <v>2021</v>
       </c>
-      <c r="D143" s="11">
+      <c r="D143" s="10">
         <f t="shared" si="2"/>
         <v>44408</v>
       </c>
@@ -7269,14 +7265,14 @@
         <v>11.330204485253018</v>
       </c>
     </row>
-    <row r="144" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B144" s="6">
+    <row r="144" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B144" s="5">
         <v>8</v>
       </c>
-      <c r="C144" s="6">
+      <c r="C144" s="5">
         <v>2021</v>
       </c>
-      <c r="D144" s="11">
+      <c r="D144" s="10">
         <f t="shared" si="2"/>
         <v>44439</v>
       </c>
@@ -7305,14 +7301,14 @@
         <v>7.5916501755334727</v>
       </c>
     </row>
-    <row r="145" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B145" s="6">
+    <row r="145" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B145" s="5">
         <v>9</v>
       </c>
-      <c r="C145" s="6">
+      <c r="C145" s="5">
         <v>2021</v>
       </c>
-      <c r="D145" s="11">
+      <c r="D145" s="10">
         <f t="shared" si="2"/>
         <v>44469</v>
       </c>
@@ -7341,14 +7337,14 @@
         <v>13.506881481661727</v>
       </c>
     </row>
-    <row r="146" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B146" s="6">
+    <row r="146" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B146" s="5">
         <v>10</v>
       </c>
-      <c r="C146" s="6">
+      <c r="C146" s="5">
         <v>2021</v>
       </c>
-      <c r="D146" s="11">
+      <c r="D146" s="10">
         <f t="shared" si="2"/>
         <v>44500</v>
       </c>
@@ -7377,14 +7373,14 @@
         <v>17.881562291072846</v>
       </c>
     </row>
-    <row r="147" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B147" s="6">
+    <row r="147" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B147" s="5">
         <v>11</v>
       </c>
-      <c r="C147" s="6">
+      <c r="C147" s="5">
         <v>2021</v>
       </c>
-      <c r="D147" s="11">
+      <c r="D147" s="10">
         <f t="shared" si="2"/>
         <v>44530</v>
       </c>
@@ -7413,14 +7409,14 @@
         <v>19.271987850792122</v>
       </c>
     </row>
-    <row r="148" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B148" s="6">
+    <row r="148" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B148" s="5">
         <v>12</v>
       </c>
-      <c r="C148" s="6">
+      <c r="C148" s="5">
         <v>2021</v>
       </c>
-      <c r="D148" s="11">
+      <c r="D148" s="10">
         <f t="shared" si="2"/>
         <v>44561</v>
       </c>
@@ -7458,14 +7454,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17D5AA4B-FF51-4BA2-8284-F92416F83C9C}">
   <dimension ref="B15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2" style="7" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="1" width="2" style="6" customWidth="1"/>
+    <col min="2" max="16384" width="9.1796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="15" spans="2:2" ht="50.25" x14ac:dyDescent="0.7">
-      <c r="B15" s="8" t="s">
+    <row r="15" spans="2:2" ht="50.5" x14ac:dyDescent="1">
+      <c r="B15" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -7478,458 +7474,457 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C5616EF-DC02-46F5-A8BF-BCC45ED435AB}">
   <dimension ref="B1:AN6"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" style="1"/>
+    <col min="3" max="3" width="7.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="2" style="1" customWidth="1"/>
-    <col min="16" max="16" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="2" style="1" customWidth="1"/>
-    <col min="29" max="30" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="36" max="37" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:40" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="4" spans="2:40" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="2:40" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <v>43496</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <v>43524</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>43555</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <v>43585</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <v>43616</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <v>43646</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <v>43677</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="11">
         <v>43708</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="11">
         <v>43738</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="11">
         <v>43769</v>
       </c>
-      <c r="M4" s="12">
+      <c r="M4" s="11">
         <v>43799</v>
       </c>
-      <c r="N4" s="12">
+      <c r="N4" s="11">
         <v>43830</v>
       </c>
-      <c r="P4" s="12">
+      <c r="P4" s="11">
         <v>43861</v>
       </c>
-      <c r="Q4" s="12">
+      <c r="Q4" s="11">
         <v>43890</v>
       </c>
-      <c r="R4" s="12">
+      <c r="R4" s="11">
         <v>43921</v>
       </c>
-      <c r="S4" s="12">
+      <c r="S4" s="11">
         <v>43951</v>
       </c>
-      <c r="T4" s="12">
+      <c r="T4" s="11">
         <v>43982</v>
       </c>
-      <c r="U4" s="12">
+      <c r="U4" s="11">
         <v>44012</v>
       </c>
-      <c r="V4" s="12">
+      <c r="V4" s="11">
         <v>44043</v>
       </c>
-      <c r="W4" s="12">
+      <c r="W4" s="11">
         <v>44074</v>
       </c>
-      <c r="X4" s="12">
+      <c r="X4" s="11">
         <v>44104</v>
       </c>
-      <c r="Y4" s="12">
+      <c r="Y4" s="11">
         <v>44135</v>
       </c>
-      <c r="Z4" s="12">
+      <c r="Z4" s="11">
         <v>44165</v>
       </c>
-      <c r="AA4" s="12">
+      <c r="AA4" s="11">
         <v>44196</v>
       </c>
-      <c r="AC4" s="12">
+      <c r="AC4" s="11">
         <v>44227</v>
       </c>
-      <c r="AD4" s="12">
+      <c r="AD4" s="11">
         <v>44255</v>
       </c>
-      <c r="AE4" s="12">
+      <c r="AE4" s="11">
         <v>44286</v>
       </c>
-      <c r="AF4" s="12">
+      <c r="AF4" s="11">
         <v>44316</v>
       </c>
-      <c r="AG4" s="12">
+      <c r="AG4" s="11">
         <v>44347</v>
       </c>
-      <c r="AH4" s="12">
+      <c r="AH4" s="11">
         <v>44377</v>
       </c>
-      <c r="AI4" s="12">
+      <c r="AI4" s="11">
         <v>44408</v>
       </c>
-      <c r="AJ4" s="12">
+      <c r="AJ4" s="11">
         <v>44439</v>
       </c>
-      <c r="AK4" s="12">
+      <c r="AK4" s="11">
         <v>44469</v>
       </c>
-      <c r="AL4" s="12">
+      <c r="AL4" s="11">
         <v>44500</v>
       </c>
-      <c r="AM4" s="12">
+      <c r="AM4" s="11">
         <v>44530</v>
       </c>
-      <c r="AN4" s="12">
+      <c r="AN4" s="11">
         <v>44561</v>
       </c>
     </row>
-    <row r="5" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!C$4,Database!$F:$F)</f>
         <v>1941.2307692307691</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!D$4,Database!$F:$F)</f>
         <v>1849.4690780228509</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!E$4,Database!$F:$F)</f>
         <v>2175.2769230769227</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!F$4,Database!$F:$F)</f>
         <v>2080.8114935648005</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!G$4,Database!$F:$F)</f>
         <v>2249.1230769230765</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!H$4,Database!$F:$F)</f>
         <v>2268.6</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!I$4,Database!$F:$F)</f>
         <v>2498.3076923076919</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!J$4,Database!$F:$F)</f>
         <v>1462.7392706420908</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!K$4,Database!$F:$F)</f>
         <v>2334.9230769230767</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!L$4,Database!$F:$F)</f>
         <v>2639.8615413642956</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!M$4,Database!$F:$F)</f>
         <v>2258.8321142992068</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!N$4,Database!$F:$F)</f>
         <v>2448.0830535688224</v>
       </c>
-      <c r="P5" s="13">
+      <c r="P5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!P$4,Database!$F:$F)</f>
         <v>2660.0985011616999</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="Q5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!Q$4,Database!$F:$F)</f>
         <v>2301.820609688868</v>
       </c>
-      <c r="R5" s="13">
+      <c r="R5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!R$4,Database!$F:$F)</f>
         <v>2545.2376374103087</v>
       </c>
-      <c r="S5" s="13">
+      <c r="S5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!S$4,Database!$F:$F)</f>
         <v>2850.2724207650704</v>
       </c>
-      <c r="T5" s="13">
+      <c r="T5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!T$4,Database!$F:$F)</f>
         <v>3038.4310200419095</v>
       </c>
-      <c r="U5" s="13">
+      <c r="U5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!U$4,Database!$F:$F)</f>
         <v>3081.4457503043245</v>
       </c>
-      <c r="V5" s="13">
+      <c r="V5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!V$4,Database!$F:$F)</f>
         <v>3239.2990697390751</v>
       </c>
-      <c r="W5" s="13">
+      <c r="W5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!W$4,Database!$F:$F)</f>
         <v>1844.6118688762529</v>
       </c>
-      <c r="X5" s="13">
+      <c r="X5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!X$4,Database!$F:$F)</f>
         <v>2926.9243830603632</v>
       </c>
-      <c r="Y5" s="13">
+      <c r="Y5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!Y$4,Database!$F:$F)</f>
         <v>3382.5564278401821</v>
       </c>
-      <c r="Z5" s="13">
+      <c r="Z5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!Z$4,Database!$F:$F)</f>
         <v>3102.5376031076216</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="AA5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AA$4,Database!$F:$F)</f>
         <v>2853.3720012781246</v>
       </c>
-      <c r="AC5" s="13">
+      <c r="AC5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AC$4,Database!$F:$F)</f>
         <v>3363.3852773606832</v>
       </c>
-      <c r="AD5" s="13">
+      <c r="AD5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AD$4,Database!$F:$F)</f>
         <v>2896.4020535350955</v>
       </c>
-      <c r="AE5" s="13">
+      <c r="AE5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AE$4,Database!$F:$F)</f>
         <v>3365.879258708992</v>
       </c>
-      <c r="AF5" s="13">
+      <c r="AF5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AF$4,Database!$F:$F)</f>
         <v>3715.4704340513654</v>
       </c>
-      <c r="AG5" s="13">
+      <c r="AG5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AG$4,Database!$F:$F)</f>
         <v>4039.0341221931335</v>
       </c>
-      <c r="AH5" s="13">
+      <c r="AH5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AH$4,Database!$F:$F)</f>
         <v>3971.8638408805</v>
       </c>
-      <c r="AI5" s="13">
+      <c r="AI5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AI$4,Database!$F:$F)</f>
         <v>4245.9215971449739</v>
       </c>
-      <c r="AJ5" s="13">
+      <c r="AJ5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AJ$4,Database!$F:$F)</f>
         <v>2486.2807465538858</v>
       </c>
-      <c r="AK5" s="13">
+      <c r="AK5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AK$4,Database!$F:$F)</f>
         <v>3863.1103827011807</v>
       </c>
-      <c r="AL5" s="13">
+      <c r="AL5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AL$4,Database!$F:$F)</f>
         <v>4289.1516580473954</v>
       </c>
-      <c r="AM5" s="13">
+      <c r="AM5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AM$4,Database!$F:$F)</f>
         <v>4193.7394584541544</v>
       </c>
-      <c r="AN5" s="13">
+      <c r="AN5" s="12">
         <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AN$4,Database!$F:$F)</f>
         <v>3799.390432295012</v>
       </c>
     </row>
-    <row r="6" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!C$4,Database!$G:$G)</f>
         <v>706.15384615384608</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!D$4,Database!$G:$G)</f>
         <v>600</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!E$4,Database!$G:$G)</f>
         <v>710.76923076923072</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!F$4,Database!$G:$G)</f>
         <v>656.30769230769238</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!G$4,Database!$G:$G)</f>
         <v>670.61538461538453</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!H$4,Database!$G:$G)</f>
         <v>593.53846153846155</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!I$4,Database!$G:$G)</f>
         <v>583.38461538461536</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!J$4,Database!$G:$G)</f>
         <v>474.46153846153845</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!K$4,Database!$G:$G)</f>
         <v>639.69230769230762</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!L$4,Database!$G:$G)</f>
         <v>676.61538461538453</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!M$4,Database!$G:$G)</f>
         <v>571.38461538461536</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!N$4,Database!$G:$G)</f>
         <v>422.76923076923066</v>
       </c>
-      <c r="P6" s="13">
+      <c r="P6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!P$4,Database!$G:$G)</f>
         <v>596.71949207527507</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="Q6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!Q$4,Database!$G:$G)</f>
         <v>504.42901070568638</v>
       </c>
-      <c r="R6" s="13">
+      <c r="R6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!R$4,Database!$G:$G)</f>
         <v>596.36058786890646</v>
       </c>
-      <c r="S6" s="13">
+      <c r="S6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!S$4,Database!$G:$G)</f>
         <v>726.58170848780583</v>
       </c>
-      <c r="T6" s="13">
+      <c r="T6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!T$4,Database!$G:$G)</f>
         <v>705.03445476861111</v>
       </c>
-      <c r="U6" s="13">
+      <c r="U6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!U$4,Database!$G:$G)</f>
         <v>683.74813890747942</v>
       </c>
-      <c r="V6" s="13">
+      <c r="V6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!V$4,Database!$G:$G)</f>
         <v>612.10540577172105</v>
       </c>
-      <c r="W6" s="13">
+      <c r="W6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!W$4,Database!$G:$G)</f>
         <v>509.49498696850935</v>
       </c>
-      <c r="X6" s="13">
+      <c r="X6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!X$4,Database!$G:$G)</f>
         <v>716.91889176476468</v>
       </c>
-      <c r="Y6" s="13">
+      <c r="Y6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!Y$4,Database!$G:$G)</f>
         <v>731.14755311591955</v>
       </c>
-      <c r="Z6" s="13">
+      <c r="Z6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!Z$4,Database!$G:$G)</f>
         <v>590.71973108505404</v>
       </c>
-      <c r="AA6" s="13">
+      <c r="AA6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AA$4,Database!$G:$G)</f>
         <v>589.9854844016553</v>
       </c>
-      <c r="AC6" s="13">
+      <c r="AC6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AC$4,Database!$G:$G)</f>
         <v>830.40526365672724</v>
       </c>
-      <c r="AD6" s="13">
+      <c r="AD6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AD$4,Database!$G:$G)</f>
         <v>681.69872570104417</v>
       </c>
-      <c r="AE6" s="13">
+      <c r="AE6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AE$4,Database!$G:$G)</f>
         <v>881.25703792407626</v>
       </c>
-      <c r="AF6" s="13">
+      <c r="AF6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AF$4,Database!$G:$G)</f>
         <v>962.77009739234722</v>
       </c>
-      <c r="AG6" s="13">
+      <c r="AG6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AG$4,Database!$G:$G)</f>
         <v>984.26685700500332</v>
       </c>
-      <c r="AH6" s="13">
+      <c r="AH6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AH$4,Database!$G:$G)</f>
         <v>892.57693620058262</v>
       </c>
-      <c r="AI6" s="13">
+      <c r="AI6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AI$4,Database!$G:$G)</f>
         <v>849.00258706451814</v>
       </c>
-      <c r="AJ6" s="13">
+      <c r="AJ6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AJ$4,Database!$G:$G)</f>
         <v>651.03464179819332</v>
       </c>
-      <c r="AK6" s="13">
+      <c r="AK6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AK$4,Database!$G:$G)</f>
         <v>969.92134547183161</v>
       </c>
-      <c r="AL6" s="13">
+      <c r="AL6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AL$4,Database!$G:$G)</f>
         <v>912.00556711908484</v>
       </c>
-      <c r="AM6" s="13">
+      <c r="AM6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AM$4,Database!$G:$G)</f>
         <v>886.19585760204654</v>
       </c>
-      <c r="AN6" s="13">
+      <c r="AN6" s="12">
         <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AN$4,Database!$G:$G)</f>
         <v>799.51580878156631</v>
       </c>
@@ -7944,25 +7939,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6806D4A5-53CC-4EE4-9048-325F21B2D152}">
   <dimension ref="B1:H8"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="9.1796875" style="1"/>
+    <col min="3" max="3" width="7.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C3" s="1">
         <v>2020</v>
       </c>
@@ -7976,105 +7971,105 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="2:8" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$C:$C,'2. Comparative analysis'!C$3,Database!$E:$E,'2. Comparative analysis'!C$4)</f>
         <v>28425.842968554865</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$C:$C,'2. Comparative analysis'!D$3,Database!$E:$E,'2. Comparative analysis'!D$4)</f>
         <v>1453.8325384615384</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$C:$C,'2. Comparative analysis'!E$3,Database!$E:$E,'2. Comparative analysis'!E$4)</f>
         <v>2527.9539230769228</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$C:$C,'2. Comparative analysis'!F$3,Database!$E:$E,'2. Comparative analysis'!F$4)</f>
         <v>1418.97786318047</v>
       </c>
-      <c r="H5" s="13"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="12"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="12">
         <f>SUMIFS(Database!$G:$G,Database!$C:$C,'2. Comparative analysis'!C$3,Database!$E:$E,'2. Comparative analysis'!C$4)</f>
         <v>-5741.8060487947223</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <f>SUMIFS(Database!$G:$G,Database!$C:$C,'2. Comparative analysis'!D$3,Database!$E:$E,'2. Comparative analysis'!D$4)</f>
         <v>-365.53846153846149</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <f>SUMIFS(Database!$G:$G,Database!$C:$C,'2. Comparative analysis'!E$3,Database!$E:$E,'2. Comparative analysis'!E$4)</f>
         <v>-475.38461538461524</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <f>SUMIFS(Database!$G:$G,Database!$C:$C,'2. Comparative analysis'!F$3,Database!$E:$E,'2. Comparative analysis'!F$4)</f>
         <v>-980.51632020358954</v>
       </c>
-      <c r="H6" s="13"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="12"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="12">
         <f>SUM(C5:C6)</f>
         <v>22684.036919760143</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <f t="shared" ref="D7:F7" si="0">SUM(D5:D6)</f>
         <v>1088.294076923077</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <f t="shared" si="0"/>
         <v>2052.5693076923076</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <f t="shared" si="0"/>
         <v>438.46154297688042</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B8" s="15" t="s">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="15">
         <f>C7/C5</f>
         <v>0.79800753648198219</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="15">
         <f>D7/D5</f>
         <v>0.74856907390085092</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="15">
         <f>E7/E5</f>
         <v>0.81194886067939231</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <f>F7/F5</f>
         <v>0.3089981558937932</v>
       </c>
@@ -8088,52 +8083,52 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E17FCAD-CCDF-436D-9A7D-9C663632857A}">
   <dimension ref="B1:E12"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="1" customWidth="1"/>
-    <col min="3" max="5" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="5" width="9.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="4" spans="2:5" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="2:5" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="12">
         <f>1.1*D5</f>
         <v>23256.062500000004</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <v>21141.875</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <f>D5*0.85</f>
         <v>17970.59375</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
@@ -8147,72 +8142,72 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B7" s="17" t="s">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="17">
         <f>C5*C6</f>
         <v>32558.487500000003</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <v>33827</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="17">
         <f>E5*E6</f>
         <v>32347.068750000002</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B8" s="23"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-    </row>
-    <row r="9" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="5" t="s">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="21"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="19">
         <v>-0.33</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="19">
         <v>-0.35</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="19">
         <v>-0.39</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B10" s="17" t="s">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="17">
         <f>C9*C5</f>
         <v>-7674.5006250000015</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <f>D9*D5</f>
         <v>-7399.6562499999991</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="17">
         <f>E9*E5</f>
         <v>-7008.5315625000003</v>
       </c>
     </row>
-    <row r="12" spans="2:5" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="19" t="s">
+    <row r="12" spans="2:5" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="20">
         <f>C7+C10</f>
         <v>24883.986875000002</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="20">
         <f>D7+D10</f>
         <v>26427.34375</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="20">
         <f>E7+E10</f>
         <v>25338.537187500002</v>
       </c>
@@ -8226,36 +8221,36 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C394F4-BEDB-4AB1-A69E-27F25541FC63}">
   <dimension ref="B1:U40"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="1.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="1"/>
+    <col min="2" max="2" width="9.54296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="1.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1796875" style="1"/>
     <col min="7" max="7" width="2" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" style="1" customWidth="1"/>
-    <col min="10" max="10" width="1.42578125" style="1" customWidth="1"/>
-    <col min="11" max="13" width="9.140625" style="1"/>
-    <col min="14" max="14" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="1.42578125" style="1" customWidth="1"/>
-    <col min="16" max="17" width="9.140625" style="1"/>
-    <col min="18" max="18" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.7109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="1.42578125" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="10" width="1.453125" style="1" customWidth="1"/>
+    <col min="11" max="13" width="9.1796875" style="1"/>
+    <col min="14" max="14" width="20.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="1.453125" style="1" customWidth="1"/>
+    <col min="16" max="17" width="9.1796875" style="1"/>
+    <col min="18" max="18" width="8.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.7265625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="1.453125" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
@@ -8281,1404 +8276,1402 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="2:21" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9" t="s">
+      <c r="E4" s="8"/>
+      <c r="F4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9" t="s">
+      <c r="J4" s="8"/>
+      <c r="K4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9" t="s">
+      <c r="O4" s="8"/>
+      <c r="P4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="R4" s="9" t="s">
+      <c r="R4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="S4" s="9" t="s">
+      <c r="S4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9" t="s">
+      <c r="T4" s="8"/>
+      <c r="U4" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B5" s="25">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B5" s="23">
         <v>43496</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B5,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>1801.8461538461538</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B5,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>317.56003295633286</v>
       </c>
-      <c r="E5" s="26"/>
-      <c r="F5" s="20">
+      <c r="E5" s="12"/>
+      <c r="F5" s="19">
         <f>CORREL(C5:C40,D5:D40)</f>
         <v>0.53730053770623409</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B5,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>1801.8461538461538</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B5,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>252.92307692307693</v>
       </c>
-      <c r="K5" s="20">
+      <c r="K5" s="19">
         <f>CORREL(H5:H40,I5:I40)</f>
         <v>0.7020388059591236</v>
       </c>
-      <c r="M5" s="26">
+      <c r="M5" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B5,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>1801.8461538461538</v>
       </c>
-      <c r="N5" s="26">
+      <c r="N5" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B5,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.8083589743589745</v>
       </c>
-      <c r="P5" s="20">
+      <c r="P5" s="19">
         <f>CORREL(M5:M40,N5:N40)</f>
         <v>0.46619427565139515</v>
       </c>
-      <c r="R5" s="26">
+      <c r="R5" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B5,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>1801.8461538461538</v>
       </c>
-      <c r="S5" s="26">
+      <c r="S5" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B5,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>69.025004250191103</v>
       </c>
-      <c r="U5" s="20">
+      <c r="U5" s="19">
         <f>CORREL(R5:R40,S5:S40)</f>
         <v>0.76929154798445498</v>
       </c>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B6" s="25">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B6" s="23">
         <v>43524</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B6,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>1705.1921549459278</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B6,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>316.66867665156281</v>
       </c>
-      <c r="E6" s="27"/>
-      <c r="H6" s="26">
+      <c r="E6" s="4"/>
+      <c r="H6" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B6,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>1705.1921549459278</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B6,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>259.38461538461536</v>
       </c>
-      <c r="M6" s="26">
+      <c r="M6" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B6,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>1705.1921549459278</v>
       </c>
-      <c r="N6" s="26">
+      <c r="N6" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B6,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.6003393665158376</v>
       </c>
-      <c r="R6" s="26">
+      <c r="R6" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B6,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>1705.1921549459278</v>
       </c>
-      <c r="S6" s="26">
+      <c r="S6" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B6,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>57.520836875159247</v>
       </c>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B7" s="25">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B7" s="23">
         <v>43555</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B7,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2013.2307692307691</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B7,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>318.15531964770105</v>
       </c>
-      <c r="E7" s="24"/>
-      <c r="H7" s="26">
+      <c r="E7" s="22"/>
+      <c r="H7" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B7,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2013.2307692307691</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B7,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>277.84615384615381</v>
       </c>
-      <c r="M7" s="26">
+      <c r="M7" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B7,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2013.2307692307691</v>
       </c>
-      <c r="N7" s="26">
+      <c r="N7" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B7,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.1106932126696831</v>
       </c>
-      <c r="R7" s="26">
+      <c r="R7" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B7,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2013.2307692307691</v>
       </c>
-      <c r="S7" s="26">
+      <c r="S7" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B7,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>60.851039057917099</v>
       </c>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B8" s="25">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B8" s="23">
         <v>43585</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B8,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>1908.7038012571081</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B8,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>323.66212377591722</v>
       </c>
-      <c r="E8" s="24"/>
-      <c r="H8" s="26">
+      <c r="E8" s="22"/>
+      <c r="H8" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B8,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>1908.7038012571081</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B8,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>294.46153846153845</v>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B8,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>1908.7038012571081</v>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B8,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.9171692307692294</v>
       </c>
-      <c r="R8" s="26">
+      <c r="R8" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B8,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>1908.7038012571081</v>
       </c>
-      <c r="S8" s="26">
+      <c r="S8" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B8,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>64.960981617215637</v>
       </c>
     </row>
-    <row r="9" spans="2:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="25">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B9" s="23">
         <v>43616</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B9,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2069.0769230769229</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B9,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>350.6167207078031</v>
       </c>
-      <c r="E9" s="22"/>
-      <c r="H9" s="26">
+      <c r="E9" s="19"/>
+      <c r="H9" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B9,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2069.0769230769229</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B9,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>298.15384615384613</v>
       </c>
-      <c r="M9" s="26">
+      <c r="M9" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B9,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2069.0769230769229</v>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B9,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.9171692307692307</v>
       </c>
-      <c r="R9" s="26">
+      <c r="R9" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B9,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2069.0769230769229</v>
       </c>
-      <c r="S9" s="26">
+      <c r="S9" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B9,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>64.960981617215637</v>
       </c>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B10" s="25">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B10" s="23">
         <v>43646</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B10,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2093.0769230769229</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B10,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>349.06431904555728</v>
       </c>
-      <c r="E10" s="24"/>
-      <c r="H10" s="26">
+      <c r="E10" s="22"/>
+      <c r="H10" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B10,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2093.0769230769229</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B10,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>308.30769230769232</v>
       </c>
-      <c r="M10" s="26">
+      <c r="M10" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B10,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2093.0769230769229</v>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B10,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.9171692307692294</v>
       </c>
-      <c r="R10" s="26">
+      <c r="R10" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B10,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2093.0769230769229</v>
       </c>
-      <c r="S10" s="26">
+      <c r="S10" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B10,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>71.706858378858712</v>
       </c>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B11" s="25">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B11" s="23">
         <v>43677</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B11,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2299.3846153846152</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B11,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>306.5846153846154</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="H11" s="26">
+      <c r="H11" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B11,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2299.3846153846152</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B11,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>334.15384615384613</v>
       </c>
-      <c r="M11" s="26">
+      <c r="M11" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B11,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2299.3846153846152</v>
       </c>
-      <c r="N11" s="26">
+      <c r="N11" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B11,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.9171692307692294</v>
       </c>
-      <c r="R11" s="26">
+      <c r="R11" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B11,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2299.3846153846152</v>
       </c>
-      <c r="S11" s="26">
+      <c r="S11" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B11,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>71.706858378858712</v>
       </c>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B12" s="25">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B12" s="23">
         <v>43708</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B12,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>1311.8161937190139</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B12,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="24"/>
-      <c r="H12" s="26">
+      <c r="E12" s="22"/>
+      <c r="H12" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B12,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>1311.8161937190139</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B12,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>309.23076923076923</v>
       </c>
-      <c r="M12" s="26">
+      <c r="M12" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B12,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>1311.8161937190139</v>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B12,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.9171692307692307</v>
       </c>
-      <c r="R12" s="26">
+      <c r="R12" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B12,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>1311.8161937190139</v>
       </c>
-      <c r="S12" s="26">
+      <c r="S12" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B12,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>71.706858378858712</v>
       </c>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B13" s="25">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B13" s="23">
         <v>43738</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B13,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2004.9230769230769</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B13,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>336.17902097902095</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="H13" s="26">
+      <c r="H13" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B13,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2004.9230769230769</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B13,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>258.46153846153845</v>
       </c>
-      <c r="M13" s="26">
+      <c r="M13" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B13,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2004.9230769230769</v>
       </c>
-      <c r="N13" s="26">
+      <c r="N13" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B13,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.9171692307692307</v>
       </c>
-      <c r="R13" s="26">
+      <c r="R13" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B13,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2004.9230769230769</v>
       </c>
-      <c r="S13" s="26">
+      <c r="S13" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B13,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>71.706858378858712</v>
       </c>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B14" s="25">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B14" s="23">
         <v>43769</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B14,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2302.1538461538457</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B14,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>430.54809176804645</v>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B14,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2302.1538461538457</v>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B14,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>331.38461538461536</v>
       </c>
-      <c r="M14" s="26">
+      <c r="M14" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B14,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2302.1538461538457</v>
       </c>
-      <c r="N14" s="26">
+      <c r="N14" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B14,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.9171692307692307</v>
       </c>
-      <c r="R14" s="26">
+      <c r="R14" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B14,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2302.1538461538457</v>
       </c>
-      <c r="S14" s="26">
+      <c r="S14" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B14,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>68.706787320924349</v>
       </c>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B15" s="25">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B15" s="23">
         <v>43799</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B15,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>1940.0013450684376</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B15,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>142.21037501151409</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B15,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>1940.0013450684376</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B15,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>339.69230769230768</v>
       </c>
-      <c r="M15" s="26">
+      <c r="M15" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B15,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>1940.0013450684376</v>
       </c>
-      <c r="N15" s="26">
+      <c r="N15" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B15,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.9171692307692307</v>
       </c>
-      <c r="R15" s="26">
+      <c r="R15" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B15,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>1940.0013450684376</v>
       </c>
-      <c r="S15" s="26">
+      <c r="S15" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B15,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>68.706787320924349</v>
       </c>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B16" s="25">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B16" s="23">
         <v>43830</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B16,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2205.0830535688219</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B16,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>216.85185163033373</v>
       </c>
-      <c r="H16" s="26">
+      <c r="H16" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B16,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2205.0830535688219</v>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B16,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>426.46153846153845</v>
       </c>
-      <c r="M16" s="26">
+      <c r="M16" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B16,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2205.0830535688219</v>
       </c>
-      <c r="N16" s="26">
+      <c r="N16" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B16,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.9171692307692307</v>
       </c>
-      <c r="R16" s="26">
+      <c r="R16" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B16,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2205.0830535688219</v>
       </c>
-      <c r="S16" s="26">
+      <c r="S16" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B16,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>68.706787320924349</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B17" s="25">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B17" s="23">
         <v>43861</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B17,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2297.3547793846155</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B17,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>429.75179897867866</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B17,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2297.3547793846155</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B17,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>306.50442156268923</v>
       </c>
-      <c r="M17" s="26">
+      <c r="M17" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B17,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2297.3547793846155</v>
       </c>
-      <c r="N17" s="26">
+      <c r="N17" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B17,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.9226097435897436</v>
       </c>
-      <c r="R17" s="26">
+      <c r="R17" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B17,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2297.3547793846155</v>
       </c>
-      <c r="S17" s="26">
+      <c r="S17" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B17,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>78.155624371879711</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B18" s="25">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B18" s="23">
         <v>43890</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B18,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>1898.7291700615385</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B18,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>295.23095674846701</v>
       </c>
-      <c r="H18" s="26">
+      <c r="H18" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B18,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>1898.7291700615385</v>
       </c>
-      <c r="I18" s="26">
+      <c r="I18" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B18,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>296.3505754088431</v>
       </c>
-      <c r="M18" s="26">
+      <c r="M18" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B18,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>1898.7291700615385</v>
       </c>
-      <c r="N18" s="26">
+      <c r="N18" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B18,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.7083495475113124</v>
       </c>
-      <c r="R18" s="26">
+      <c r="R18" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B18,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>1898.7291700615385</v>
       </c>
-      <c r="S18" s="26">
+      <c r="S18" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B18,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>65.129686976566433</v>
       </c>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B19" s="25">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B19" s="23">
         <v>43921</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B19,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2131.5160541538462</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B19,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>355.03679592091459</v>
       </c>
-      <c r="H19" s="26">
+      <c r="H19" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B19,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2131.5160541538462</v>
       </c>
-      <c r="I19" s="26">
+      <c r="I19" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B19,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>282.2274984857662</v>
       </c>
-      <c r="M19" s="26">
+      <c r="M19" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B19,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2131.5160541538462</v>
       </c>
-      <c r="N19" s="26">
+      <c r="N19" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B19,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.2040140090497733</v>
       </c>
-      <c r="R19" s="26">
+      <c r="R19" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B19,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2131.5160541538462</v>
       </c>
-      <c r="S19" s="26">
+      <c r="S19" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B19,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>75.274039028579637</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B20" s="25">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B20" s="23">
         <v>43951</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B20,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2381.6399300526346</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B20,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>355.88069238920195</v>
       </c>
-      <c r="H20" s="26">
+      <c r="H20" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B20,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2381.6399300526346</v>
       </c>
-      <c r="I20" s="26">
+      <c r="I20" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B20,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>359.84474356978387</v>
       </c>
-      <c r="M20" s="26">
+      <c r="M20" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B20,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2381.6399300526346</v>
       </c>
-      <c r="N20" s="26">
+      <c r="N20" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B20,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.0346843076923076</v>
       </c>
-      <c r="R20" s="26">
+      <c r="R20" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B20,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2381.6399300526346</v>
       </c>
-      <c r="S20" s="26">
+      <c r="S20" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B20,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>75.274039028579637</v>
       </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B21" s="25">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B21" s="23">
         <v>43982</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B21,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2596.4210828211262</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B21,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>359.96446666274915</v>
       </c>
-      <c r="H21" s="26">
+      <c r="H21" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B21,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2596.4210828211262</v>
       </c>
-      <c r="I21" s="26">
+      <c r="I21" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B21,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>358.22818814256135</v>
       </c>
-      <c r="M21" s="26">
+      <c r="M21" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B21,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2596.4210828211262</v>
       </c>
-      <c r="N21" s="26">
+      <c r="N21" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B21,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.0346843076923076</v>
       </c>
-      <c r="R21" s="26">
+      <c r="R21" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B21,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2596.4210828211262</v>
       </c>
-      <c r="S21" s="26">
+      <c r="S21" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B21,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>75.274039028579637</v>
       </c>
     </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B22" s="25">
+    <row r="22" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B22" s="23">
         <v>44012</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B22,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2585.4275982306776</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B22,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>358.20659736380242</v>
       </c>
-      <c r="H22" s="26">
+      <c r="H22" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B22,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2585.4275982306776</v>
       </c>
-      <c r="I22" s="26">
+      <c r="I22" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B22,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>359.7601346389788</v>
       </c>
-      <c r="M22" s="26">
+      <c r="M22" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B22,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2585.4275982306776</v>
       </c>
-      <c r="N22" s="26">
+      <c r="N22" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B22,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.0346843076923076</v>
       </c>
-      <c r="R22" s="26">
+      <c r="R22" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B22,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2585.4275982306776</v>
       </c>
-      <c r="S22" s="26">
+      <c r="S22" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B22,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>84.321941536768662</v>
       </c>
     </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B23" s="25">
+    <row r="23" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B23" s="23">
         <v>44043</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B23,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2805.4668659894869</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B23,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>363.43574983680008</v>
       </c>
-      <c r="H23" s="26">
+      <c r="H23" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B23,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2805.4668659894869</v>
       </c>
-      <c r="I23" s="26">
+      <c r="I23" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B23,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>365.51924214483887</v>
       </c>
-      <c r="M23" s="26">
+      <c r="M23" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B23,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2805.4668659894869</v>
       </c>
-      <c r="N23" s="26">
+      <c r="N23" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B23,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.0346843076923076</v>
       </c>
-      <c r="R23" s="26">
+      <c r="R23" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B23,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2805.4668659894869</v>
       </c>
-      <c r="S23" s="26">
+      <c r="S23" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B23,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>84.321941536768662</v>
       </c>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B24" s="25">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B24" s="23">
         <v>44074</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B24,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>1517.3647168026064</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B24,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B24,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>1517.3647168026064</v>
       </c>
-      <c r="I24" s="26">
+      <c r="I24" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B24,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>352.59875472586475</v>
       </c>
-      <c r="M24" s="26">
+      <c r="M24" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B24,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>1517.3647168026064</v>
       </c>
-      <c r="N24" s="26">
+      <c r="N24" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B24,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.0346843076923076</v>
       </c>
-      <c r="R24" s="26">
+      <c r="R24" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B24,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>1517.3647168026064</v>
       </c>
-      <c r="S24" s="26">
+      <c r="S24" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B24,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>84.321941536768662</v>
       </c>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B25" s="25">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B25" s="23">
         <v>44104</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B25,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2387.7385182449816</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B25,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>341.53992007336234</v>
       </c>
-      <c r="H25" s="26">
+      <c r="H25" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B25,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2387.7385182449816</v>
       </c>
-      <c r="I25" s="26">
+      <c r="I25" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B25,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>358.10139595165975</v>
       </c>
-      <c r="M25" s="26">
+      <c r="M25" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B25,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2387.7385182449816</v>
       </c>
-      <c r="N25" s="26">
+      <c r="N25" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B25,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.0346843076923076</v>
       </c>
-      <c r="R25" s="26">
+      <c r="R25" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B25,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2387.7385182449816</v>
       </c>
-      <c r="S25" s="26">
+      <c r="S25" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B25,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>84.321941536768662</v>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B26" s="25">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B26" s="23">
         <v>44135</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B26,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2811.3204398297107</v>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B26,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>346.56430418643265</v>
       </c>
-      <c r="H26" s="26">
+      <c r="H26" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B26,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2811.3204398297107</v>
       </c>
-      <c r="I26" s="26">
+      <c r="I26" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B26,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>363.00460447193706</v>
       </c>
-      <c r="M26" s="26">
+      <c r="M26" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B26,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2811.3204398297107</v>
       </c>
-      <c r="N26" s="26">
+      <c r="N26" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B26,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.0346843076923076</v>
       </c>
-      <c r="R26" s="26">
+      <c r="R26" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B26,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2811.3204398297107</v>
       </c>
-      <c r="S26" s="26">
+      <c r="S26" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B26,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>76.996142597335265</v>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B27" s="25">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B27" s="23">
         <v>44165</v>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B27,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2631.3002650596682</v>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B27,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>343.50299125468251</v>
       </c>
-      <c r="H27" s="26">
+      <c r="H27" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B27,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2631.3002650596682</v>
       </c>
-      <c r="I27" s="26">
+      <c r="I27" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B27,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>360.1750715269668</v>
       </c>
-      <c r="M27" s="26">
+      <c r="M27" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B27,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2631.3002650596682</v>
       </c>
-      <c r="N27" s="26">
+      <c r="N27" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B27,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.0346843076923067</v>
       </c>
-      <c r="R27" s="26">
+      <c r="R27" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B27,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2631.3002650596682</v>
       </c>
-      <c r="S27" s="26">
+      <c r="S27" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B27,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>76.996142597335265</v>
       </c>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B28" s="25">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B28" s="23">
         <v>44196</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B28,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2381.5635479239754</v>
       </c>
-      <c r="D28" s="26">
+      <c r="D28" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B28,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>349.14882134792106</v>
       </c>
-      <c r="H28" s="26">
+      <c r="H28" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B28,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2381.5635479239754</v>
       </c>
-      <c r="I28" s="26">
+      <c r="I28" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B28,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>357.92733166699941</v>
       </c>
-      <c r="M28" s="26">
+      <c r="M28" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B28,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2381.5635479239754</v>
       </c>
-      <c r="N28" s="26">
+      <c r="N28" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B28,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.0346843076923076</v>
       </c>
-      <c r="R28" s="26">
+      <c r="R28" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B28,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2381.5635479239754</v>
       </c>
-      <c r="S28" s="26">
+      <c r="S28" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B28,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>80.67956081669594</v>
       </c>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B29" s="25">
+    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B29" s="23">
         <v>44227</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B29,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2874.629079449584</v>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B29,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>570.05035081036954</v>
       </c>
-      <c r="H29" s="26">
+      <c r="H29" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B29,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2874.629079449584</v>
       </c>
-      <c r="I29" s="26">
+      <c r="I29" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B29,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>380.06481278116303</v>
       </c>
-      <c r="M29" s="26">
+      <c r="M29" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B29,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2874.629079449584</v>
       </c>
-      <c r="N29" s="26">
+      <c r="N29" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B29,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.0402880358974356</v>
       </c>
-      <c r="R29" s="26">
+      <c r="R29" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B29,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2874.629079449584</v>
       </c>
-      <c r="S29" s="26">
+      <c r="S29" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B29,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>101.59504890398503</v>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B30" s="25">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B30" s="23">
         <v>44255</v>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B30,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2371.1521492234538</v>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B30,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>387.92593239906603</v>
       </c>
-      <c r="H30" s="26">
+      <c r="H30" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B30,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2371.1521492234538</v>
       </c>
-      <c r="I30" s="26">
+      <c r="I30" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B30,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>334.87483141523575</v>
       </c>
-      <c r="M30" s="26">
+      <c r="M30" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B30,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2371.1521492234538</v>
       </c>
-      <c r="N30" s="26">
+      <c r="N30" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B30,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.8196000339366525</v>
       </c>
-      <c r="R30" s="26">
+      <c r="R30" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B30,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2371.1521492234538</v>
       </c>
-      <c r="S30" s="26">
+      <c r="S30" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B30,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>85.647647017909222</v>
       </c>
     </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B31" s="25">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B31" s="23">
         <v>44286</v>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B31,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2653.0003239858484</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B31,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>345.90059127174897</v>
       </c>
-      <c r="H31" s="26">
+      <c r="H31" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B31,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2653.0003239858484</v>
       </c>
-      <c r="I31" s="26">
+      <c r="I31" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B31,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>322.1923696443244</v>
       </c>
-      <c r="M31" s="26">
+      <c r="M31" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B31,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2653.0003239858484</v>
       </c>
-      <c r="N31" s="26">
+      <c r="N31" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B31,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>3.3001344293212669</v>
       </c>
-      <c r="R31" s="26">
+      <c r="R31" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B31,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2653.0003239858484</v>
       </c>
-      <c r="S31" s="26">
+      <c r="S31" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B31,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>97.037630199114446</v>
       </c>
     </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B32" s="25">
+    <row r="32" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B32" s="23">
         <v>44316</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B32,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>3059.2684000019522</v>
       </c>
-      <c r="D32" s="26">
+      <c r="D32" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B32,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>356.44535395829075</v>
       </c>
-      <c r="H32" s="26">
+      <c r="H32" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B32,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>3059.2684000019522</v>
       </c>
-      <c r="I32" s="26">
+      <c r="I32" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B32,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>396.69110199505917</v>
       </c>
-      <c r="M32" s="26">
+      <c r="M32" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B32,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>3059.2684000019522</v>
       </c>
-      <c r="N32" s="26">
+      <c r="N32" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B32,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.1557248369230768</v>
       </c>
-      <c r="R32" s="26">
+      <c r="R32" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B32,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>3059.2684000019522</v>
       </c>
-      <c r="S32" s="26">
+      <c r="S32" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B32,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>98.916233982605618</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B33" s="25">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B33" s="23">
         <v>44347</v>
       </c>
-      <c r="C33" s="26">
+      <c r="C33" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B33,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>3358.7830600735756</v>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B33,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>364.35942067984263</v>
       </c>
-      <c r="H33" s="26">
+      <c r="H33" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B33,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>3358.7830600735756</v>
       </c>
-      <c r="I33" s="26">
+      <c r="I33" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B33,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>392.38056878084097</v>
       </c>
-      <c r="M33" s="26">
+      <c r="M33" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B33,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>3358.7830600735756</v>
       </c>
-      <c r="N33" s="26">
+      <c r="N33" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B33,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.1557248369230768</v>
       </c>
-      <c r="R33" s="26">
+      <c r="R33" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B33,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>3358.7830600735756</v>
       </c>
-      <c r="S33" s="26">
+      <c r="S33" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B33,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>105.802493123179</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B34" s="25">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B34" s="23">
         <v>44377</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B34,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>3293.0867506235236</v>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B34,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>357.79217119087212</v>
       </c>
-      <c r="H34" s="26">
+      <c r="H34" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B34,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>3293.0867506235236</v>
       </c>
-      <c r="I34" s="26">
+      <c r="I34" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B34,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>390.18462893269481</v>
       </c>
-      <c r="M34" s="26">
+      <c r="M34" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B34,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>3293.0867506235236</v>
       </c>
-      <c r="N34" s="26">
+      <c r="N34" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B34,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.1557248369230768</v>
       </c>
-      <c r="R34" s="26">
+      <c r="R34" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B34,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>3293.0867506235236</v>
       </c>
-      <c r="S34" s="26">
+      <c r="S34" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B34,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B35" s="25">
+    <row r="35" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B35" s="23">
         <v>44408</v>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B35,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>3557.447872674275</v>
       </c>
-      <c r="D35" s="26">
+      <c r="D35" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B35,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>361.83155406279531</v>
       </c>
-      <c r="H35" s="26">
+      <c r="H35" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B35,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>3557.447872674275</v>
       </c>
-      <c r="I35" s="26">
+      <c r="I35" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B35,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>393.61176892029539</v>
       </c>
-      <c r="M35" s="26">
+      <c r="M35" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B35,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>3557.447872674275</v>
       </c>
-      <c r="N35" s="26">
+      <c r="N35" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B35,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.1557248369230768</v>
       </c>
-      <c r="R35" s="26">
+      <c r="R35" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B35,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>3557.447872674275</v>
       </c>
-      <c r="S35" s="26">
+      <c r="S35" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B35,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="36" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B36" s="25">
+    <row r="36" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B36" s="23">
         <v>44439</v>
       </c>
-      <c r="C36" s="26">
+      <c r="C36" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B36,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>2003.0740472156231</v>
       </c>
-      <c r="D36" s="26">
+      <c r="D36" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B36,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>0</v>
       </c>
-      <c r="H36" s="26">
+      <c r="H36" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B36,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>2003.0740472156231</v>
       </c>
-      <c r="I36" s="26">
+      <c r="I36" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B36,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>383.96104709133749</v>
       </c>
-      <c r="M36" s="26">
+      <c r="M36" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B36,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>2003.0740472156231</v>
       </c>
-      <c r="N36" s="26">
+      <c r="N36" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B36,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.1557248369230777</v>
       </c>
-      <c r="R36" s="26">
+      <c r="R36" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B36,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>2003.0740472156231</v>
       </c>
-      <c r="S36" s="26">
+      <c r="S36" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B36,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B37" s="25">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B37" s="23">
         <v>44469</v>
       </c>
-      <c r="C37" s="26">
+      <c r="C37" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B37,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>3101.115697960674</v>
       </c>
-      <c r="D37" s="26">
+      <c r="D37" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B37,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>338.90228325765707</v>
       </c>
-      <c r="H37" s="26">
+      <c r="H37" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B37,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>3101.115697960674</v>
       </c>
-      <c r="I37" s="26">
+      <c r="I37" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B37,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>383.72765347003684</v>
       </c>
-      <c r="M37" s="26">
+      <c r="M37" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B37,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>3101.115697960674</v>
       </c>
-      <c r="N37" s="26">
+      <c r="N37" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B37,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.1557248369230777</v>
       </c>
-      <c r="R37" s="26">
+      <c r="R37" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B37,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>3101.115697960674</v>
       </c>
-      <c r="S37" s="26">
+      <c r="S37" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B37,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B38" s="25">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B38" s="23">
         <v>44500</v>
       </c>
-      <c r="C38" s="26">
+      <c r="C38" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B38,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>3585.5364248185365</v>
       </c>
-      <c r="D38" s="26">
+      <c r="D38" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B38,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>343.83882484613252</v>
       </c>
-      <c r="H38" s="26">
+      <c r="H38" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B38,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>3585.5364248185365</v>
       </c>
-      <c r="I38" s="26">
+      <c r="I38" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B38,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>388.57135682844063</v>
       </c>
-      <c r="M38" s="26">
+      <c r="M38" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B38,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>3585.5364248185365</v>
       </c>
-      <c r="N38" s="26">
+      <c r="N38" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B38,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.1557248369230777</v>
       </c>
-      <c r="R38" s="26">
+      <c r="R38" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B38,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>3585.5364248185365</v>
       </c>
-      <c r="S38" s="26">
+      <c r="S38" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B38,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>102.40669860582705</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B39" s="25">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B39" s="23">
         <v>44530</v>
       </c>
-      <c r="C39" s="26">
+      <c r="C39" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B39,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>3342.6306670456706</v>
       </c>
-      <c r="D39" s="26">
+      <c r="D39" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B39,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>337.17177766757521</v>
       </c>
-      <c r="H39" s="26">
+      <c r="H39" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B39,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>3342.6306670456706</v>
       </c>
-      <c r="I39" s="26">
+      <c r="I39" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B39,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>388.42288981285924</v>
       </c>
-      <c r="M39" s="26">
+      <c r="M39" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B39,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>3342.6306670456706</v>
       </c>
-      <c r="N39" s="26">
+      <c r="N39" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B39,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.1557248369230777</v>
       </c>
-      <c r="R39" s="26">
+      <c r="R39" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B39,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>3342.6306670456706</v>
       </c>
-      <c r="S39" s="26">
+      <c r="S39" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B39,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>102.40669860582705</v>
       </c>
     </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B40" s="25">
+    <row r="40" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B40" s="23">
         <v>44561</v>
       </c>
-      <c r="C40" s="26">
+      <c r="C40" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B40,Database!$E:$E,'4. Correlation'!C$3)</f>
         <v>3039.6080358355593</v>
       </c>
-      <c r="D40" s="26">
+      <c r="D40" s="12">
         <f>-SUMIFS(Database!$H:$H,Database!$D:$D,'4. Correlation'!$B40,Database!$E:$E,'4. Correlation'!D$3)</f>
         <v>414.7238697888377</v>
       </c>
-      <c r="H40" s="26">
+      <c r="H40" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B40,Database!$E:$E,'4. Correlation'!H$3)</f>
         <v>3039.6080358355593</v>
       </c>
-      <c r="I40" s="26">
+      <c r="I40" s="12">
         <f>-SUMIFS(Database!$I:$I,Database!$D:$D,'4. Correlation'!$B40,Database!$E:$E,'4. Correlation'!I$3)</f>
         <v>410.09087534435923</v>
       </c>
-      <c r="M40" s="26">
+      <c r="M40" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B40,Database!$E:$E,'4. Correlation'!M$3)</f>
         <v>3039.6080358355593</v>
       </c>
-      <c r="N40" s="26">
+      <c r="N40" s="12">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'4. Correlation'!$B40,Database!$E:$E,'4. Correlation'!N$3)</f>
         <v>4.1557248369230768</v>
       </c>
-      <c r="R40" s="26">
+      <c r="R40" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'4. Correlation'!$B40,Database!$E:$E,'4. Correlation'!R$3)</f>
         <v>3039.6080358355593</v>
       </c>
-      <c r="S40" s="26">
+      <c r="S40" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'4. Correlation'!$B40,Database!$E:$E,'4. Correlation'!S$3)</f>
         <v>99.258185203903267</v>
       </c>
@@ -9692,28 +9685,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDDE9806-ADB7-48CD-8C59-AC7EEA475D2F}">
   <dimension ref="B1:AD40"/>
-  <sheetFormatPr defaultRowHeight="12" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="9.140625" style="1"/>
+    <col min="2" max="2" width="9.54296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="9.1796875" style="1"/>
     <col min="11" max="14" width="0" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="9.140625" style="1" collapsed="1"/>
-    <col min="16" max="25" width="9.140625" style="1"/>
+    <col min="15" max="15" width="9.1796875" style="1" collapsed="1"/>
+    <col min="16" max="25" width="9.1796875" style="1"/>
     <col min="26" max="29" width="0" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="30" max="30" width="9.140625" style="1" collapsed="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="9.1796875" style="1" collapsed="1"/>
+    <col min="31" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:29" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:29" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="3" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:29" x14ac:dyDescent="0.25">
       <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
@@ -9727,55 +9720,55 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:29" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="2:29" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="Q4" s="9" t="s">
+      <c r="Q4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="R4" s="9" t="s">
+      <c r="R4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="S4" s="9" t="s">
+      <c r="S4" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="U4" s="9" t="s">
+      <c r="U4" s="8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B5" s="25">
+    <row r="5" spans="2:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B5" s="23">
         <v>43496</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B5,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>1801.8461538461538</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="Q5" s="25">
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="Q5" s="23">
         <v>43496</v>
       </c>
-      <c r="R5" s="26">
+      <c r="R5" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B5,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>1801.8461538461538</v>
       </c>
@@ -9791,35 +9784,35 @@
       <c r="AB5"/>
       <c r="AC5"/>
     </row>
-    <row r="6" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="25">
+    <row r="6" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="23">
         <v>43524</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B6,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>1705.1921549459278</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <f>C5</f>
         <v>1801.8461538461538</v>
       </c>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="Q6" s="25">
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="Q6" s="23">
         <v>43524</v>
       </c>
-      <c r="R6" s="26">
+      <c r="R6" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B6,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>1705.1921549459278</v>
       </c>
-      <c r="S6" s="13"/>
+      <c r="S6" s="12"/>
       <c r="U6"/>
       <c r="V6"/>
       <c r="W6"/>
@@ -9830,41 +9823,41 @@
       <c r="AB6"/>
       <c r="AC6"/>
     </row>
-    <row r="7" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B7" s="25">
+    <row r="7" spans="2:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B7" s="23">
         <v>43555</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B7,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2013.2307692307691</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <f t="shared" ref="D7:D40" si="0">C6</f>
         <v>1705.1921549459278</v>
       </c>
-      <c r="F7" s="34" t="s">
+      <c r="F7" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="34"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="33"/>
-      <c r="Q7" s="25">
+      <c r="G7" s="29"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="Q7" s="23">
         <v>43555</v>
       </c>
-      <c r="R7" s="26">
+      <c r="R7" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B7,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2013.2307692307691</v>
       </c>
-      <c r="S7" s="13"/>
-      <c r="U7" s="32" t="s">
+      <c r="S7" s="12"/>
+      <c r="U7" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="V7" s="32"/>
+      <c r="V7" s="27"/>
       <c r="W7"/>
       <c r="X7"/>
       <c r="Y7"/>
@@ -9873,43 +9866,43 @@
       <c r="AB7"/>
       <c r="AC7"/>
     </row>
-    <row r="8" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B8" s="25">
+    <row r="8" spans="2:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B8" s="23">
         <v>43585</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B8,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>1908.7038012571081</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <f t="shared" si="0"/>
         <v>2013.2307692307691</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="35">
+      <c r="G8" s="28">
         <v>0.56162008028695454</v>
       </c>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="Q8" s="25">
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="Q8" s="23">
         <v>43585</v>
       </c>
-      <c r="R8" s="26">
+      <c r="R8" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B8,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>1908.7038012571081</v>
       </c>
-      <c r="S8" s="13"/>
-      <c r="U8" s="29" t="s">
+      <c r="S8" s="12"/>
+      <c r="U8" t="s">
         <v>37</v>
       </c>
-      <c r="V8" s="29">
+      <c r="V8">
         <v>0.96609541391591747</v>
       </c>
       <c r="W8"/>
@@ -9920,43 +9913,43 @@
       <c r="AB8"/>
       <c r="AC8"/>
     </row>
-    <row r="9" spans="2:29" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="25">
+    <row r="9" spans="2:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B9" s="23">
         <v>43616</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B9,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2069.0769230769229</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <f t="shared" si="0"/>
         <v>1908.7038012571081</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="28">
         <v>0.31541711458152527</v>
       </c>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="Q9" s="25">
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="Q9" s="23">
         <v>43616</v>
       </c>
-      <c r="R9" s="26">
+      <c r="R9" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B9,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2069.0769230769229</v>
       </c>
-      <c r="S9" s="13"/>
-      <c r="U9" s="29" t="s">
+      <c r="S9" s="12"/>
+      <c r="U9" t="s">
         <v>38</v>
       </c>
-      <c r="V9" s="29">
+      <c r="V9">
         <v>0.93334034878936789</v>
       </c>
       <c r="W9"/>
@@ -9967,43 +9960,43 @@
       <c r="AB9"/>
       <c r="AC9"/>
     </row>
-    <row r="10" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="25">
+    <row r="10" spans="2:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B10" s="23">
         <v>43646</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B10,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2093.0769230769229</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="12">
         <f t="shared" si="0"/>
         <v>2069.0769230769229</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="28">
         <v>0.29467217865975331</v>
       </c>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="Q10" s="25">
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="Q10" s="23">
         <v>43646</v>
       </c>
-      <c r="R10" s="26">
+      <c r="R10" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B10,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2093.0769230769229</v>
       </c>
-      <c r="S10" s="13"/>
-      <c r="U10" s="29" t="s">
+      <c r="S10" s="12"/>
+      <c r="U10" t="s">
         <v>39</v>
       </c>
-      <c r="V10" s="29">
+      <c r="V10">
         <v>0.93031036464343009</v>
       </c>
       <c r="W10"/>
@@ -10014,43 +10007,43 @@
       <c r="AB10"/>
       <c r="AC10"/>
     </row>
-    <row r="11" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B11" s="25">
+    <row r="11" spans="2:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B11" s="23">
         <v>43677</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B11,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2299.3846153846152</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <f t="shared" si="0"/>
         <v>2093.0769230769229</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="28">
         <v>482.30409560006422</v>
       </c>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="Q11" s="25">
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="Q11" s="23">
         <v>43677</v>
       </c>
-      <c r="R11" s="26">
+      <c r="R11" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B11,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2299.3846153846152</v>
       </c>
-      <c r="S11" s="13"/>
-      <c r="U11" s="29" t="s">
+      <c r="S11" s="12"/>
+      <c r="U11" t="s">
         <v>40</v>
       </c>
-      <c r="V11" s="29">
+      <c r="V11">
         <v>141.70842027773412</v>
       </c>
       <c r="W11"/>
@@ -10061,43 +10054,43 @@
       <c r="AB11"/>
       <c r="AC11"/>
     </row>
-    <row r="12" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="25">
+    <row r="12" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="23">
         <v>43708</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B12,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>1311.8161937190139</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="12">
         <f t="shared" si="0"/>
         <v>2299.3846153846152</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="30">
         <v>35</v>
       </c>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="Q12" s="25">
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="Q12" s="23">
         <v>43708</v>
       </c>
-      <c r="R12" s="26">
+      <c r="R12" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B12,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>1311.8161937190139</v>
       </c>
-      <c r="S12" s="13"/>
-      <c r="U12" s="30" t="s">
+      <c r="S12" s="12"/>
+      <c r="U12" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="V12" s="30">
+      <c r="V12" s="25">
         <v>24</v>
       </c>
       <c r="W12"/>
@@ -10108,35 +10101,35 @@
       <c r="AB12"/>
       <c r="AC12"/>
     </row>
-    <row r="13" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B13" s="25">
+    <row r="13" spans="2:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B13" s="23">
         <v>43738</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B13,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2004.9230769230769</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <f t="shared" si="0"/>
         <v>1311.8161937190139</v>
       </c>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="Q13" s="25">
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="Q13" s="23">
         <v>43738</v>
       </c>
-      <c r="R13" s="26">
+      <c r="R13" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B13,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2004.9230769230769</v>
       </c>
-      <c r="S13" s="13"/>
+      <c r="S13" s="12"/>
       <c r="U13"/>
       <c r="V13"/>
       <c r="W13"/>
@@ -10147,37 +10140,37 @@
       <c r="AB13"/>
       <c r="AC13"/>
     </row>
-    <row r="14" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="25">
+    <row r="14" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="23">
         <v>43769</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B14,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2302.1538461538457</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="12">
         <f t="shared" si="0"/>
         <v>2004.9230769230769</v>
       </c>
-      <c r="F14" s="33" t="s">
+      <c r="F14" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="Q14" s="25">
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="Q14" s="23">
         <v>43769</v>
       </c>
-      <c r="R14" s="26">
+      <c r="R14" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B14,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2302.1538461538457</v>
       </c>
-      <c r="S14" s="13"/>
+      <c r="S14" s="12"/>
       <c r="U14" t="s">
         <v>42</v>
       </c>
@@ -10190,269 +10183,269 @@
       <c r="AB14"/>
       <c r="AC14"/>
     </row>
-    <row r="15" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B15" s="25">
+    <row r="15" spans="2:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="23">
         <v>43799</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B15,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>1940.0013450684376</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="12">
         <f t="shared" si="0"/>
         <v>2302.1538461538457</v>
       </c>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37" t="s">
+      <c r="F15" s="31"/>
+      <c r="G15" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="37" t="s">
+      <c r="H15" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="37" t="s">
+      <c r="I15" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="J15" s="37" t="s">
+      <c r="J15" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="K15" s="37" t="s">
+      <c r="K15" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="Q15" s="25">
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="Q15" s="23">
         <v>43799</v>
       </c>
-      <c r="R15" s="26">
+      <c r="R15" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B15,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>1940.0013450684376</v>
       </c>
-      <c r="S15" s="13"/>
-      <c r="U15" s="31"/>
-      <c r="V15" s="31" t="s">
+      <c r="S15" s="12"/>
+      <c r="U15" s="26"/>
+      <c r="V15" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="W15" s="31" t="s">
+      <c r="W15" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="X15" s="31" t="s">
+      <c r="X15" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="Y15" s="31" t="s">
+      <c r="Y15" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="Z15" s="31" t="s">
+      <c r="Z15" s="26" t="s">
         <v>51</v>
       </c>
       <c r="AA15"/>
       <c r="AB15"/>
       <c r="AC15"/>
     </row>
-    <row r="16" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B16" s="25">
+    <row r="16" spans="2:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B16" s="23">
         <v>43830</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B16,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2205.0830535688219</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="12">
         <f t="shared" si="0"/>
         <v>1940.0013450684376</v>
       </c>
-      <c r="F16" s="35" t="s">
+      <c r="F16" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="35">
+      <c r="G16" s="28">
         <v>1</v>
       </c>
-      <c r="H16" s="35">
+      <c r="H16" s="28">
         <v>3536837.0921428511</v>
       </c>
-      <c r="I16" s="35">
+      <c r="I16" s="28">
         <v>3536837.0921428511</v>
       </c>
-      <c r="J16" s="35">
+      <c r="J16" s="28">
         <v>15.204535495840828</v>
       </c>
-      <c r="K16" s="35">
+      <c r="K16" s="28">
         <v>4.473734614825491E-4</v>
       </c>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="Q16" s="25">
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="Q16" s="23">
         <v>43830</v>
       </c>
-      <c r="R16" s="26">
+      <c r="R16" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B16,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2205.0830535688219</v>
       </c>
-      <c r="S16" s="13"/>
-      <c r="U16" s="29" t="s">
+      <c r="S16" s="12"/>
+      <c r="U16" t="s">
         <v>43</v>
       </c>
-      <c r="V16" s="29">
+      <c r="V16">
         <v>1</v>
       </c>
-      <c r="W16" s="29">
+      <c r="W16">
         <v>6185730.5502877235</v>
       </c>
-      <c r="X16" s="29">
+      <c r="X16">
         <v>6185730.5502877235</v>
       </c>
-      <c r="Y16" s="29">
+      <c r="Y16">
         <v>308.03473016208955</v>
       </c>
-      <c r="Z16" s="29">
+      <c r="Z16">
         <v>2.0044021568177263E-14</v>
       </c>
       <c r="AA16"/>
       <c r="AB16"/>
       <c r="AC16"/>
     </row>
-    <row r="17" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="25">
+    <row r="17" spans="2:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B17" s="23">
         <v>43861</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B17,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2297.3547793846155</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="12">
         <f t="shared" si="0"/>
         <v>2205.0830535688219</v>
       </c>
-      <c r="F17" s="35" t="s">
+      <c r="F17" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="35">
+      <c r="G17" s="28">
         <v>33</v>
       </c>
-      <c r="H17" s="35">
+      <c r="H17" s="28">
         <v>7676368.9408756634</v>
       </c>
-      <c r="I17" s="35">
+      <c r="I17" s="28">
         <v>232617.24063259587</v>
       </c>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="Q17" s="25">
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="Q17" s="23">
         <v>43861</v>
       </c>
-      <c r="R17" s="26">
+      <c r="R17" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B17,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2297.3547793846155</v>
       </c>
-      <c r="S17" s="13">
+      <c r="S17" s="12">
         <f>R5</f>
         <v>1801.8461538461538</v>
       </c>
-      <c r="U17" s="29" t="s">
+      <c r="U17" t="s">
         <v>44</v>
       </c>
-      <c r="V17" s="29">
+      <c r="V17">
         <v>22</v>
       </c>
-      <c r="W17" s="29">
+      <c r="W17">
         <v>441788.08030744037</v>
       </c>
-      <c r="X17" s="29">
+      <c r="X17">
         <v>20081.276377610924</v>
       </c>
-      <c r="Y17" s="29"/>
-      <c r="Z17" s="29"/>
+      <c r="Y17"/>
+      <c r="Z17"/>
       <c r="AA17"/>
       <c r="AB17"/>
       <c r="AC17"/>
     </row>
-    <row r="18" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="25">
+    <row r="18" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="23">
         <v>43890</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B18,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>1898.7291700615385</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="12">
         <f t="shared" si="0"/>
         <v>2297.3547793846155</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="F18" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="G18" s="36">
+      <c r="G18" s="30">
         <v>34</v>
       </c>
-      <c r="H18" s="36">
+      <c r="H18" s="30">
         <v>11213206.033018515</v>
       </c>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="Q18" s="25">
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="Q18" s="23">
         <v>43890</v>
       </c>
-      <c r="R18" s="26">
+      <c r="R18" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B18,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>1898.7291700615385</v>
       </c>
-      <c r="S18" s="13">
+      <c r="S18" s="12">
         <f t="shared" ref="S18:S40" si="1">R6</f>
         <v>1705.1921549459278</v>
       </c>
-      <c r="U18" s="30" t="s">
+      <c r="U18" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="V18" s="30">
+      <c r="V18" s="25">
         <v>23</v>
       </c>
-      <c r="W18" s="30">
+      <c r="W18" s="25">
         <v>6627518.6305951644</v>
       </c>
-      <c r="X18" s="30"/>
-      <c r="Y18" s="30"/>
-      <c r="Z18" s="30"/>
+      <c r="X18" s="25"/>
+      <c r="Y18" s="25"/>
+      <c r="Z18" s="25"/>
       <c r="AA18"/>
       <c r="AB18"/>
       <c r="AC18"/>
     </row>
-    <row r="19" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="25">
+    <row r="19" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="23">
         <v>43921</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B19,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2131.5160541538462</v>
       </c>
-      <c r="D19" s="13">
+      <c r="D19" s="12">
         <f t="shared" si="0"/>
         <v>1898.7291700615385</v>
       </c>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="Q19" s="25">
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="Q19" s="23">
         <v>43921</v>
       </c>
-      <c r="R19" s="26">
+      <c r="R19" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B19,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2131.5160541538462</v>
       </c>
-      <c r="S19" s="13">
+      <c r="S19" s="12">
         <f t="shared" si="1"/>
         <v>2013.2307692307691</v>
       </c>
@@ -10466,265 +10459,265 @@
       <c r="AB19"/>
       <c r="AC19"/>
     </row>
-    <row r="20" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B20" s="25">
+    <row r="20" spans="2:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B20" s="23">
         <v>43951</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B20,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2381.6399300526346</v>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="12">
         <f t="shared" si="0"/>
         <v>2131.5160541538462</v>
       </c>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37" t="s">
+      <c r="F20" s="31"/>
+      <c r="G20" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="H20" s="37" t="s">
+      <c r="H20" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="I20" s="37" t="s">
+      <c r="I20" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="J20" s="37" t="s">
+      <c r="J20" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="K20" s="37" t="s">
+      <c r="K20" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="L20" s="37" t="s">
+      <c r="L20" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="M20" s="37" t="s">
+      <c r="M20" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="N20" s="37" t="s">
+      <c r="N20" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="Q20" s="25">
+      <c r="Q20" s="23">
         <v>43951</v>
       </c>
-      <c r="R20" s="26">
+      <c r="R20" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B20,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2381.6399300526346</v>
       </c>
-      <c r="S20" s="13">
+      <c r="S20" s="12">
         <f t="shared" si="1"/>
         <v>1908.7038012571081</v>
       </c>
-      <c r="U20" s="31"/>
-      <c r="V20" s="31" t="s">
+      <c r="U20" s="26"/>
+      <c r="V20" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="W20" s="31" t="s">
+      <c r="W20" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="X20" s="31" t="s">
+      <c r="X20" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="Y20" s="31" t="s">
+      <c r="Y20" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="Z20" s="31" t="s">
+      <c r="Z20" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="AA20" s="31" t="s">
+      <c r="AA20" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="AB20" s="31" t="s">
+      <c r="AB20" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="AC20" s="31" t="s">
+      <c r="AC20" s="26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B21" s="25">
+    <row r="21" spans="2:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B21" s="23">
         <v>43982</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B21,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2596.4210828211262</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="12">
         <f t="shared" si="0"/>
         <v>2381.6399300526346</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="F21" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="G21" s="35">
+      <c r="G21" s="28">
         <v>1108.5459176978243</v>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="28">
         <v>359.02874323267605</v>
       </c>
-      <c r="I21" s="35">
+      <c r="I21" s="28">
         <v>3.0876244272715736</v>
       </c>
-      <c r="J21" s="35">
+      <c r="J21" s="28">
         <v>4.0716275386512464E-3</v>
       </c>
-      <c r="K21" s="35">
+      <c r="K21" s="28">
         <v>378.09644736693372</v>
       </c>
-      <c r="L21" s="35">
+      <c r="L21" s="28">
         <v>1838.9953880287148</v>
       </c>
-      <c r="M21" s="35">
+      <c r="M21" s="28">
         <v>378.09644736693372</v>
       </c>
-      <c r="N21" s="35">
+      <c r="N21" s="28">
         <v>1838.9953880287148</v>
       </c>
-      <c r="Q21" s="25">
+      <c r="Q21" s="23">
         <v>43982</v>
       </c>
-      <c r="R21" s="26">
+      <c r="R21" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B21,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2596.4210828211262</v>
       </c>
-      <c r="S21" s="13">
+      <c r="S21" s="12">
         <f t="shared" si="1"/>
         <v>2069.0769230769229</v>
       </c>
-      <c r="U21" s="29" t="s">
+      <c r="U21" t="s">
         <v>46</v>
       </c>
-      <c r="V21" s="29">
+      <c r="V21">
         <v>-254.74427012654905</v>
       </c>
-      <c r="W21" s="29">
+      <c r="W21">
         <v>170.50418648618211</v>
       </c>
-      <c r="X21" s="29">
+      <c r="X21">
         <v>-1.494064605546761</v>
       </c>
-      <c r="Y21" s="29">
+      <c r="Y21">
         <v>0.14936412136529709</v>
       </c>
-      <c r="Z21" s="29">
+      <c r="Z21">
         <v>-608.34831044512771</v>
       </c>
-      <c r="AA21" s="29">
+      <c r="AA21">
         <v>98.859770192029544</v>
       </c>
-      <c r="AB21" s="29">
+      <c r="AB21">
         <v>-608.34831044512771</v>
       </c>
-      <c r="AC21" s="29">
+      <c r="AC21">
         <v>98.859770192029544</v>
       </c>
     </row>
-    <row r="22" spans="2:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="25">
+    <row r="22" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="23">
         <v>44012</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B22,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2585.4275982306776</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="12">
         <f t="shared" si="0"/>
         <v>2596.4210828211262</v>
       </c>
-      <c r="F22" s="36" t="s">
+      <c r="F22" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="30">
         <v>0.55955299670260028</v>
       </c>
-      <c r="H22" s="36">
+      <c r="H22" s="30">
         <v>0.14350090749606506</v>
       </c>
-      <c r="I22" s="36">
+      <c r="I22" s="30">
         <v>3.8992993596081877</v>
       </c>
-      <c r="J22" s="36">
+      <c r="J22" s="30">
         <v>4.473734614825491E-4</v>
       </c>
-      <c r="K22" s="36">
+      <c r="K22" s="30">
         <v>0.2675982052039933</v>
       </c>
-      <c r="L22" s="36">
+      <c r="L22" s="30">
         <v>0.85150778820120721</v>
       </c>
-      <c r="M22" s="36">
+      <c r="M22" s="30">
         <v>0.2675982052039933</v>
       </c>
-      <c r="N22" s="36">
+      <c r="N22" s="30">
         <v>0.85150778820120721</v>
       </c>
-      <c r="Q22" s="25">
+      <c r="Q22" s="23">
         <v>44012</v>
       </c>
-      <c r="R22" s="26">
+      <c r="R22" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B22,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2585.4275982306776</v>
       </c>
-      <c r="S22" s="13">
+      <c r="S22" s="12">
         <f t="shared" si="1"/>
         <v>2093.0769230769229</v>
       </c>
-      <c r="U22" s="30" t="s">
+      <c r="U22" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="V22" s="30">
+      <c r="V22" s="25">
         <v>1.3590358486692169</v>
       </c>
-      <c r="W22" s="30">
+      <c r="W22" s="25">
         <v>7.7433888761924599E-2</v>
       </c>
-      <c r="X22" s="30">
+      <c r="X22" s="25">
         <v>17.550918214215727</v>
       </c>
-      <c r="Y22" s="30">
+      <c r="Y22" s="25">
         <v>2.0044021568177333E-14</v>
       </c>
-      <c r="Z22" s="30">
+      <c r="Z22" s="25">
         <v>1.1984477922227852</v>
       </c>
-      <c r="AA22" s="30">
+      <c r="AA22" s="25">
         <v>1.5196239051156486</v>
       </c>
-      <c r="AB22" s="30">
+      <c r="AB22" s="25">
         <v>1.1984477922227852</v>
       </c>
-      <c r="AC22" s="30">
+      <c r="AC22" s="25">
         <v>1.5196239051156486</v>
       </c>
     </row>
-    <row r="23" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="25">
+    <row r="23" spans="2:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B23" s="23">
         <v>44043</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B23,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2805.4668659894869</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="12">
         <f t="shared" si="0"/>
         <v>2585.4275982306776</v>
       </c>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="33"/>
-      <c r="N23" s="33"/>
-      <c r="Q23" s="25">
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="Q23" s="23">
         <v>44043</v>
       </c>
-      <c r="R23" s="26">
+      <c r="R23" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B23,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2805.4668659894869</v>
       </c>
-      <c r="S23" s="13">
+      <c r="S23" s="12">
         <f t="shared" si="1"/>
         <v>2299.3846153846152</v>
       </c>
@@ -10738,15 +10731,15 @@
       <c r="AB23"/>
       <c r="AC23"/>
     </row>
-    <row r="24" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B24" s="25">
+    <row r="24" spans="2:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B24" s="23">
         <v>44074</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B24,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>1517.3647168026064</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="12">
         <f t="shared" si="0"/>
         <v>2805.4668659894869</v>
       </c>
@@ -10759,14 +10752,14 @@
       <c r="L24"/>
       <c r="M24"/>
       <c r="N24"/>
-      <c r="Q24" s="25">
+      <c r="Q24" s="23">
         <v>44074</v>
       </c>
-      <c r="R24" s="26">
+      <c r="R24" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B24,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>1517.3647168026064</v>
       </c>
-      <c r="S24" s="13">
+      <c r="S24" s="12">
         <f t="shared" si="1"/>
         <v>1311.8161937190139</v>
       </c>
@@ -10780,15 +10773,15 @@
       <c r="AB24"/>
       <c r="AC24"/>
     </row>
-    <row r="25" spans="2:29" ht="15" x14ac:dyDescent="0.25">
-      <c r="B25" s="25">
+    <row r="25" spans="2:29" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B25" s="23">
         <v>44104</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B25,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2387.7385182449816</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="12">
         <f t="shared" si="0"/>
         <v>1517.3647168026064</v>
       </c>
@@ -10801,14 +10794,14 @@
       <c r="L25"/>
       <c r="M25"/>
       <c r="N25"/>
-      <c r="Q25" s="25">
+      <c r="Q25" s="23">
         <v>44104</v>
       </c>
-      <c r="R25" s="26">
+      <c r="R25" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B25,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2387.7385182449816</v>
       </c>
-      <c r="S25" s="13">
+      <c r="S25" s="12">
         <f t="shared" si="1"/>
         <v>2004.9230769230769</v>
       </c>
@@ -10822,362 +10815,362 @@
       <c r="AB25"/>
       <c r="AC25"/>
     </row>
-    <row r="26" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B26" s="25">
+    <row r="26" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B26" s="23">
         <v>44135</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B26,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2811.3204398297107</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="12">
         <f t="shared" si="0"/>
         <v>2387.7385182449816</v>
       </c>
-      <c r="Q26" s="25">
+      <c r="Q26" s="23">
         <v>44135</v>
       </c>
-      <c r="R26" s="26">
+      <c r="R26" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B26,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2811.3204398297107</v>
       </c>
-      <c r="S26" s="13">
+      <c r="S26" s="12">
         <f t="shared" si="1"/>
         <v>2302.1538461538457</v>
       </c>
     </row>
-    <row r="27" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B27" s="25">
+    <row r="27" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B27" s="23">
         <v>44165</v>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B27,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2631.3002650596682</v>
       </c>
-      <c r="D27" s="13">
+      <c r="D27" s="12">
         <f t="shared" si="0"/>
         <v>2811.3204398297107</v>
       </c>
-      <c r="Q27" s="25">
+      <c r="Q27" s="23">
         <v>44165</v>
       </c>
-      <c r="R27" s="26">
+      <c r="R27" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B27,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2631.3002650596682</v>
       </c>
-      <c r="S27" s="13">
+      <c r="S27" s="12">
         <f t="shared" si="1"/>
         <v>1940.0013450684376</v>
       </c>
     </row>
-    <row r="28" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B28" s="25">
+    <row r="28" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B28" s="23">
         <v>44196</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B28,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2381.5635479239754</v>
       </c>
-      <c r="D28" s="13">
+      <c r="D28" s="12">
         <f t="shared" si="0"/>
         <v>2631.3002650596682</v>
       </c>
-      <c r="Q28" s="25">
+      <c r="Q28" s="23">
         <v>44196</v>
       </c>
-      <c r="R28" s="26">
+      <c r="R28" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B28,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2381.5635479239754</v>
       </c>
-      <c r="S28" s="13">
+      <c r="S28" s="12">
         <f t="shared" si="1"/>
         <v>2205.0830535688219</v>
       </c>
     </row>
-    <row r="29" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B29" s="25">
+    <row r="29" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B29" s="23">
         <v>44227</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B29,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2874.629079449584</v>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="12">
         <f t="shared" si="0"/>
         <v>2381.5635479239754</v>
       </c>
-      <c r="Q29" s="25">
+      <c r="Q29" s="23">
         <v>44227</v>
       </c>
-      <c r="R29" s="26">
+      <c r="R29" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B29,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2874.629079449584</v>
       </c>
-      <c r="S29" s="13">
+      <c r="S29" s="12">
         <f t="shared" si="1"/>
         <v>2297.3547793846155</v>
       </c>
     </row>
-    <row r="30" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B30" s="25">
+    <row r="30" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B30" s="23">
         <v>44255</v>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B30,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2371.1521492234538</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="12">
         <f t="shared" si="0"/>
         <v>2874.629079449584</v>
       </c>
-      <c r="Q30" s="25">
+      <c r="Q30" s="23">
         <v>44255</v>
       </c>
-      <c r="R30" s="26">
+      <c r="R30" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B30,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2371.1521492234538</v>
       </c>
-      <c r="S30" s="13">
+      <c r="S30" s="12">
         <f t="shared" si="1"/>
         <v>1898.7291700615385</v>
       </c>
     </row>
-    <row r="31" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B31" s="25">
+    <row r="31" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B31" s="23">
         <v>44286</v>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B31,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2653.0003239858484</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="12">
         <f t="shared" si="0"/>
         <v>2371.1521492234538</v>
       </c>
-      <c r="Q31" s="25">
+      <c r="Q31" s="23">
         <v>44286</v>
       </c>
-      <c r="R31" s="26">
+      <c r="R31" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B31,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2653.0003239858484</v>
       </c>
-      <c r="S31" s="13">
+      <c r="S31" s="12">
         <f t="shared" si="1"/>
         <v>2131.5160541538462</v>
       </c>
     </row>
-    <row r="32" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B32" s="25">
+    <row r="32" spans="2:29" x14ac:dyDescent="0.25">
+      <c r="B32" s="23">
         <v>44316</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B32,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>3059.2684000019522</v>
       </c>
-      <c r="D32" s="13">
+      <c r="D32" s="12">
         <f t="shared" si="0"/>
         <v>2653.0003239858484</v>
       </c>
-      <c r="Q32" s="25">
+      <c r="Q32" s="23">
         <v>44316</v>
       </c>
-      <c r="R32" s="26">
+      <c r="R32" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B32,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>3059.2684000019522</v>
       </c>
-      <c r="S32" s="13">
+      <c r="S32" s="12">
         <f t="shared" si="1"/>
         <v>2381.6399300526346</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B33" s="25">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B33" s="23">
         <v>44347</v>
       </c>
-      <c r="C33" s="26">
+      <c r="C33" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B33,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>3358.7830600735756</v>
       </c>
-      <c r="D33" s="13">
+      <c r="D33" s="12">
         <f t="shared" si="0"/>
         <v>3059.2684000019522</v>
       </c>
-      <c r="Q33" s="25">
+      <c r="Q33" s="23">
         <v>44347</v>
       </c>
-      <c r="R33" s="26">
+      <c r="R33" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B33,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>3358.7830600735756</v>
       </c>
-      <c r="S33" s="13">
+      <c r="S33" s="12">
         <f t="shared" si="1"/>
         <v>2596.4210828211262</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B34" s="25">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B34" s="23">
         <v>44377</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B34,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>3293.0867506235236</v>
       </c>
-      <c r="D34" s="13">
+      <c r="D34" s="12">
         <f t="shared" si="0"/>
         <v>3358.7830600735756</v>
       </c>
-      <c r="Q34" s="25">
+      <c r="Q34" s="23">
         <v>44377</v>
       </c>
-      <c r="R34" s="26">
+      <c r="R34" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B34,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>3293.0867506235236</v>
       </c>
-      <c r="S34" s="13">
+      <c r="S34" s="12">
         <f t="shared" si="1"/>
         <v>2585.4275982306776</v>
       </c>
     </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B35" s="25">
+    <row r="35" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B35" s="23">
         <v>44408</v>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B35,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>3557.447872674275</v>
       </c>
-      <c r="D35" s="13">
+      <c r="D35" s="12">
         <f t="shared" si="0"/>
         <v>3293.0867506235236</v>
       </c>
-      <c r="Q35" s="25">
+      <c r="Q35" s="23">
         <v>44408</v>
       </c>
-      <c r="R35" s="26">
+      <c r="R35" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B35,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>3557.447872674275</v>
       </c>
-      <c r="S35" s="13">
+      <c r="S35" s="12">
         <f t="shared" si="1"/>
         <v>2805.4668659894869</v>
       </c>
     </row>
-    <row r="36" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B36" s="25">
+    <row r="36" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B36" s="23">
         <v>44439</v>
       </c>
-      <c r="C36" s="26">
+      <c r="C36" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B36,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>2003.0740472156231</v>
       </c>
-      <c r="D36" s="13">
+      <c r="D36" s="12">
         <f t="shared" si="0"/>
         <v>3557.447872674275</v>
       </c>
-      <c r="Q36" s="25">
+      <c r="Q36" s="23">
         <v>44439</v>
       </c>
-      <c r="R36" s="26">
+      <c r="R36" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B36,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>2003.0740472156231</v>
       </c>
-      <c r="S36" s="13">
+      <c r="S36" s="12">
         <f t="shared" si="1"/>
         <v>1517.3647168026064</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B37" s="25">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B37" s="23">
         <v>44469</v>
       </c>
-      <c r="C37" s="26">
+      <c r="C37" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B37,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>3101.115697960674</v>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="12">
         <f t="shared" si="0"/>
         <v>2003.0740472156231</v>
       </c>
-      <c r="Q37" s="25">
+      <c r="Q37" s="23">
         <v>44469</v>
       </c>
-      <c r="R37" s="26">
+      <c r="R37" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B37,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>3101.115697960674</v>
       </c>
-      <c r="S37" s="13">
+      <c r="S37" s="12">
         <f t="shared" si="1"/>
         <v>2387.7385182449816</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B38" s="25">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B38" s="23">
         <v>44500</v>
       </c>
-      <c r="C38" s="26">
+      <c r="C38" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B38,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>3585.5364248185365</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="12">
         <f t="shared" si="0"/>
         <v>3101.115697960674</v>
       </c>
-      <c r="Q38" s="25">
+      <c r="Q38" s="23">
         <v>44500</v>
       </c>
-      <c r="R38" s="26">
+      <c r="R38" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B38,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>3585.5364248185365</v>
       </c>
-      <c r="S38" s="13">
+      <c r="S38" s="12">
         <f t="shared" si="1"/>
         <v>2811.3204398297107</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B39" s="25">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B39" s="23">
         <v>44530</v>
       </c>
-      <c r="C39" s="26">
+      <c r="C39" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B39,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>3342.6306670456706</v>
       </c>
-      <c r="D39" s="13">
+      <c r="D39" s="12">
         <f t="shared" si="0"/>
         <v>3585.5364248185365</v>
       </c>
-      <c r="Q39" s="25">
+      <c r="Q39" s="23">
         <v>44530</v>
       </c>
-      <c r="R39" s="26">
+      <c r="R39" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B39,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>3342.6306670456706</v>
       </c>
-      <c r="S39" s="13">
+      <c r="S39" s="12">
         <f t="shared" si="1"/>
         <v>2631.3002650596682</v>
       </c>
     </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B40" s="25">
+    <row r="40" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B40" s="23">
         <v>44561</v>
       </c>
-      <c r="C40" s="26">
+      <c r="C40" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B40,Database!$E:$E,'5. Time series'!C$3)</f>
         <v>3039.6080358355593</v>
       </c>
-      <c r="D40" s="13">
+      <c r="D40" s="12">
         <f t="shared" si="0"/>
         <v>3342.6306670456706</v>
       </c>
-      <c r="Q40" s="25">
+      <c r="Q40" s="23">
         <v>44561</v>
       </c>
-      <c r="R40" s="26">
+      <c r="R40" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'5. Time series'!$B40,Database!$E:$E,'5. Time series'!R$3)</f>
         <v>3039.6080358355593</v>
       </c>
-      <c r="S40" s="13">
+      <c r="S40" s="12">
         <f t="shared" si="1"/>
         <v>2381.5635479239754</v>
       </c>
@@ -11190,24 +11183,34 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC11A06B-9194-44FA-BAC3-7F9993C80CA2}">
-  <dimension ref="B1:E40"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:O40"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="9.54296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1796875" style="1"/>
+    <col min="7" max="7" width="17.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
@@ -11218,628 +11221,931 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:5" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="2:15" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B5" s="25">
+    <row r="5" spans="2:15" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B5" s="23">
         <v>43496</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B5,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>1801.8461538461538</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B5,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.8083589743589745</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B5,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>69.025004250191103</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B6" s="25">
+      <c r="G5" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+    </row>
+    <row r="6" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="23">
         <v>43524</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B6,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>1705.1921549459278</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B6,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.6003393665158376</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B6,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>57.520836875159247</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B7" s="25">
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+    </row>
+    <row r="7" spans="2:15" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B7" s="23">
         <v>43555</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B7,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2013.2307692307691</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B7,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.1106932126696831</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B7,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>60.851039057917099</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B8" s="25">
+      <c r="G7" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="29"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+    </row>
+    <row r="8" spans="2:15" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B8" s="23">
         <v>43585</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B8,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>1908.7038012571081</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B8,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.9171692307692294</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B8,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>64.960981617215637</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="25">
+      <c r="G8" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="32">
+        <v>0.46619427565139515</v>
+      </c>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+    </row>
+    <row r="9" spans="2:15" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B9" s="23">
         <v>43616</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B9,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2069.0769230769229</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B9,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.9171692307692307</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B9,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>64.960981617215637</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B10" s="25">
+      <c r="G9" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="32">
+        <v>0.21733710265012901</v>
+      </c>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+    </row>
+    <row r="10" spans="2:15" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B10" s="23">
         <v>43646</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B10,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2093.0769230769229</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B10,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.9171692307692294</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B10,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>71.706858378858712</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B11" s="25">
+      <c r="G10" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="32">
+        <v>0.19431760566925044</v>
+      </c>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+    </row>
+    <row r="11" spans="2:15" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B11" s="23">
         <v>43677</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B11,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2299.3846153846152</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B11,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.9171692307692294</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B11,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>71.706858378858712</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B12" s="25">
+      <c r="G11" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="32">
+        <v>517.85279640005592</v>
+      </c>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+    </row>
+    <row r="12" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="23">
         <v>43708</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B12,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>1311.8161937190139</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B12,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.9171692307692307</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B12,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>71.706858378858712</v>
       </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B13" s="25">
+      <c r="G12" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="33">
+        <v>36</v>
+      </c>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+    </row>
+    <row r="13" spans="2:15" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B13" s="23">
         <v>43738</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B13,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2004.9230769230769</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B13,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.9171692307692307</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B13,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>71.706858378858712</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B14" s="25">
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+    </row>
+    <row r="14" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="23">
         <v>43769</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B14,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2302.1538461538457</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B14,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.9171692307692307</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B14,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>68.706787320924349</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B15" s="25">
+      <c r="G14" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+    </row>
+    <row r="15" spans="2:15" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="23">
         <v>43799</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B15,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>1940.0013450684376</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B15,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.9171692307692307</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B15,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>68.706787320924349</v>
       </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B16" s="25">
+      <c r="G15" s="31"/>
+      <c r="H15" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="L15" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+    </row>
+    <row r="16" spans="2:15" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B16" s="23">
         <v>43830</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B16,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2205.0830535688219</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B16,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.9171692307692307</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B16,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>68.706787320924349</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B17" s="25">
+      <c r="G16" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="32">
+        <v>1</v>
+      </c>
+      <c r="I16" s="32">
+        <v>2531924.1747337412</v>
+      </c>
+      <c r="J16" s="32">
+        <v>2531924.1747337412</v>
+      </c>
+      <c r="K16" s="32">
+        <v>9.4414357894380956</v>
+      </c>
+      <c r="L16" s="32">
+        <v>4.1598321132618465E-3</v>
+      </c>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+    </row>
+    <row r="17" spans="2:15" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B17" s="23">
         <v>43861</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B17,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2297.3547793846155</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B17,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.9226097435897436</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B17,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>78.155624371879711</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B18" s="25">
+      <c r="G17" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="32">
+        <v>34</v>
+      </c>
+      <c r="I17" s="32">
+        <v>9117831.6371381637</v>
+      </c>
+      <c r="J17" s="32">
+        <v>268171.51873935777</v>
+      </c>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+    </row>
+    <row r="18" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="23">
         <v>43890</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B18,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>1898.7291700615385</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B18,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.7083495475113124</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B18,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>65.129686976566433</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B19" s="25">
+      <c r="G18" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="33">
+        <v>35</v>
+      </c>
+      <c r="I18" s="33">
+        <v>11649755.811871905</v>
+      </c>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+    </row>
+    <row r="19" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="23">
         <v>43921</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B19,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2131.5160541538462</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B19,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.2040140090497733</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B19,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>75.274039028579637</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B20" s="25">
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+    </row>
+    <row r="20" spans="2:15" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B20" s="23">
         <v>43951</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B20,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2381.6399300526346</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B20,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.0346843076923076</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B20,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>75.274039028579637</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B21" s="25">
+      <c r="G20" s="31"/>
+      <c r="H20" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="J20" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="K20" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="L20" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="M20" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="N20" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="O20" s="31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B21" s="23">
         <v>43982</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B21,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2596.4210828211262</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B21,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.0346843076923076</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B21,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>75.274039028579637</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B22" s="25">
+      <c r="G21" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="H21" s="32">
+        <v>-1625.3982728990431</v>
+      </c>
+      <c r="I21" s="32">
+        <v>1330.2130460685862</v>
+      </c>
+      <c r="J21" s="32">
+        <v>-1.2219082331983362</v>
+      </c>
+      <c r="K21" s="32">
+        <v>0.23014661442694018</v>
+      </c>
+      <c r="L21" s="32">
+        <v>-4328.716431994726</v>
+      </c>
+      <c r="M21" s="32">
+        <v>1077.9198861966393</v>
+      </c>
+      <c r="N21" s="32">
+        <v>-4328.716431994726</v>
+      </c>
+      <c r="O21" s="32">
+        <v>1077.9198861966393</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="23">
         <v>44012</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B22,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2585.4275982306776</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B22,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.0346843076923076</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B22,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>84.321941536768662</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B23" s="25">
+      <c r="G22" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" s="33">
+        <v>1037.8238009599597</v>
+      </c>
+      <c r="I22" s="33">
+        <v>337.75719125290311</v>
+      </c>
+      <c r="J22" s="33">
+        <v>3.0726919450927883</v>
+      </c>
+      <c r="K22" s="33">
+        <v>4.1598321132618387E-3</v>
+      </c>
+      <c r="L22" s="33">
+        <v>351.4186035536726</v>
+      </c>
+      <c r="M22" s="33">
+        <v>1724.2289983662467</v>
+      </c>
+      <c r="N22" s="33">
+        <v>351.4186035536726</v>
+      </c>
+      <c r="O22" s="33">
+        <v>1724.2289983662467</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B23" s="23">
         <v>44043</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B23,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2805.4668659894869</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B23,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.0346843076923076</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B23,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>84.321941536768662</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B24" s="25">
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+    </row>
+    <row r="24" spans="2:15" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B24" s="23">
         <v>44074</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B24,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>1517.3647168026064</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B24,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.0346843076923076</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B24,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>84.321941536768662</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B25" s="25">
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="28"/>
+      <c r="N24" s="28"/>
+      <c r="O24" s="28"/>
+    </row>
+    <row r="25" spans="2:15" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B25" s="23">
         <v>44104</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B25,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2387.7385182449816</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B25,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.0346843076923076</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B25,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>84.321941536768662</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B26" s="25">
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B26" s="23">
         <v>44135</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B26,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2811.3204398297107</v>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B26,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.0346843076923076</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B26,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>76.996142597335265</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B27" s="25">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B27" s="23">
         <v>44165</v>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B27,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2631.3002650596682</v>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B27,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.0346843076923067</v>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B27,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>76.996142597335265</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B28" s="25">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B28" s="23">
         <v>44196</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B28,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2381.5635479239754</v>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B28,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.0346843076923076</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B28,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>80.67956081669594</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B29" s="25">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B29" s="23">
         <v>44227</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B29,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2874.629079449584</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B29,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.0402880358974356</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B29,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>101.59504890398503</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B30" s="25">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B30" s="23">
         <v>44255</v>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B30,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2371.1521492234538</v>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B30,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.8196000339366525</v>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B30,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>85.647647017909222</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B31" s="25">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B31" s="23">
         <v>44286</v>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B31,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2653.0003239858484</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B31,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>3.3001344293212669</v>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B31,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>97.037630199114446</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B32" s="25">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B32" s="23">
         <v>44316</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B32,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>3059.2684000019522</v>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B32,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.1557248369230768</v>
       </c>
-      <c r="E32" s="26">
+      <c r="E32" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B32,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>98.916233982605618</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B33" s="25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="23">
         <v>44347</v>
       </c>
-      <c r="C33" s="26">
+      <c r="C33" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B33,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>3358.7830600735756</v>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B33,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.1557248369230768</v>
       </c>
-      <c r="E33" s="26">
+      <c r="E33" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B33,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>105.802493123179</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B34" s="25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="23">
         <v>44377</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B34,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>3293.0867506235236</v>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B34,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.1557248369230768</v>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B34,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B35" s="25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35" s="23">
         <v>44408</v>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B35,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>3557.447872674275</v>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B35,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.1557248369230768</v>
       </c>
-      <c r="E35" s="26">
+      <c r="E35" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B35,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B36" s="25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B36" s="23">
         <v>44439</v>
       </c>
-      <c r="C36" s="26">
+      <c r="C36" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B36,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>2003.0740472156231</v>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B36,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.1557248369230777</v>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B36,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B37" s="25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="23">
         <v>44469</v>
       </c>
-      <c r="C37" s="26">
+      <c r="C37" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B37,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>3101.115697960674</v>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B37,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.1557248369230777</v>
       </c>
-      <c r="E37" s="26">
+      <c r="E37" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B37,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B38" s="25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B38" s="23">
         <v>44500</v>
       </c>
-      <c r="C38" s="26">
+      <c r="C38" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B38,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>3585.5364248185365</v>
       </c>
-      <c r="D38" s="27">
+      <c r="D38" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B38,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.1557248369230777</v>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B38,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>102.40669860582705</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B39" s="25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="23">
         <v>44530</v>
       </c>
-      <c r="C39" s="26">
+      <c r="C39" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B39,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>3342.6306670456706</v>
       </c>
-      <c r="D39" s="27">
+      <c r="D39" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B39,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.1557248369230777</v>
       </c>
-      <c r="E39" s="26">
+      <c r="E39" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B39,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>102.40669860582705</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B40" s="25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B40" s="23">
         <v>44561</v>
       </c>
-      <c r="C40" s="26">
+      <c r="C40" s="12">
         <f>SUMIFS(Database!$F:$F,Database!$D:$D,'6.1 Regression'!$B40,Database!$E:$E,'6.1 Regression'!C$3)</f>
         <v>3039.6080358355593</v>
       </c>
-      <c r="D40" s="27">
+      <c r="D40" s="4">
         <f>SUMIFS(Database!$K:$K,Database!$D:$D,'6.1 Regression'!$B40,Database!$E:$E,'6.1 Regression'!D$3)</f>
         <v>4.1557248369230768</v>
       </c>
-      <c r="E40" s="26">
+      <c r="E40" s="12">
         <f>SUMIFS(Database!$L:$L,Database!$D:$D,'6.1 Regression'!$B40,Database!$E:$E,'6.1 Regression'!E$3)</f>
         <v>99.258185203903267</v>
       </c>
